--- a/public/templates/lens-marketing-data-template.xlsx
+++ b/public/templates/lens-marketing-data-template.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marketing data" sheetId="1" r:id="R1edc0564b5e14274"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example data" sheetId="2" r:id="R623e2ae2f3154081"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R08c26d4d4f7c46c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marketing data" sheetId="1" r:id="R40412b134bfa4fd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example data" sheetId="2" r:id="R5f8afa45a0e643f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R8cf5f87410404bb1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,10 +15,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="#,##0"/>
     <x:numFmt numFmtId="202" formatCode="&quot;£&quot;#,##0.00"/>
+    <x:numFmt numFmtId="203" formatCode="@"/>
   </x:numFmts>
   <x:fonts count="6">
     <x:font>
@@ -39,7 +40,7 @@
     <x:font>
       <x:b/>
       <x:sz val="17"/>
-      <x:color rgb="FF362B79"/>
+      <x:color rgb="FF142D4E"/>
       <x:name val="Arial"/>
     </x:font>
     <x:font>
@@ -51,7 +52,7 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FF51439C"/>
+      <x:color rgb="FF17365B"/>
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
@@ -64,7 +65,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF51439C"/>
+        <x:fgColor rgb="FF17365B"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -79,7 +80,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -96,6 +97,7 @@
     <x:xf numFmtId="202" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -108,8 +110,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MarketingInputs" displayName="MarketingInputs" ref="A1:U101" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="21">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MarketingInputs" displayName="MarketingInputs" ref="A1:X101" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="24">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Channel"/>
     <x:tableColumn id="3" name="Campaign"/>
@@ -131,14 +133,17 @@
     <x:tableColumn id="19" name="Budget"/>
     <x:tableColumn id="20" name="Email opens"/>
     <x:tableColumn id="21" name="Website traffic"/>
+    <x:tableColumn id="22" name="Platform"/>
+    <x:tableColumn id="23" name="Placement"/>
+    <x:tableColumn id="24" name="Campaign ID"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MarketingExamples" displayName="MarketingExamples" ref="A1:U101" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="21">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MarketingExamples" displayName="MarketingExamples" ref="A1:X101" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="24">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Channel"/>
     <x:tableColumn id="3" name="Campaign"/>
@@ -160,6 +165,9 @@
     <x:tableColumn id="19" name="Budget"/>
     <x:tableColumn id="20" name="Email opens"/>
     <x:tableColumn id="21" name="Website traffic"/>
+    <x:tableColumn id="22" name="Platform"/>
+    <x:tableColumn id="23" name="Placement"/>
+    <x:tableColumn id="24" name="Campaign ID"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -381,6 +389,9 @@
     <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="18" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="23" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="23" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="23" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -446,6 +457,15 @@
       </x:c>
       <x:c r="U1" s="5" t="str">
         <x:v>Website traffic</x:v>
+      </x:c>
+      <x:c r="V1" s="5" t="str">
+        <x:v>Platform</x:v>
+      </x:c>
+      <x:c r="W1" s="5" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="X1" s="5" t="str">
+        <x:v>Campaign ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="23" customHeight="1">
@@ -470,6 +490,9 @@
       <x:c r="S2" s="9"/>
       <x:c r="T2" s="8"/>
       <x:c r="U2" s="8"/>
+      <x:c r="V2" s="12"/>
+      <x:c r="W2" s="12"/>
+      <x:c r="X2" s="12"/>
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="7"/>
@@ -493,6 +516,9 @@
       <x:c r="S3" s="9"/>
       <x:c r="T3" s="8"/>
       <x:c r="U3" s="8"/>
+      <x:c r="V3" s="12"/>
+      <x:c r="W3" s="12"/>
+      <x:c r="X3" s="12"/>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="7"/>
@@ -516,6 +542,9 @@
       <x:c r="S4" s="9"/>
       <x:c r="T4" s="8"/>
       <x:c r="U4" s="8"/>
+      <x:c r="V4" s="12"/>
+      <x:c r="W4" s="12"/>
+      <x:c r="X4" s="12"/>
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
       <x:c r="A5" s="7"/>
@@ -539,6 +568,9 @@
       <x:c r="S5" s="9"/>
       <x:c r="T5" s="8"/>
       <x:c r="U5" s="8"/>
+      <x:c r="V5" s="12"/>
+      <x:c r="W5" s="12"/>
+      <x:c r="X5" s="12"/>
     </x:row>
     <x:row r="6" ht="23" customHeight="1">
       <x:c r="A6" s="7"/>
@@ -562,6 +594,9 @@
       <x:c r="S6" s="9"/>
       <x:c r="T6" s="8"/>
       <x:c r="U6" s="8"/>
+      <x:c r="V6" s="12"/>
+      <x:c r="W6" s="12"/>
+      <x:c r="X6" s="12"/>
     </x:row>
     <x:row r="7" ht="23" customHeight="1">
       <x:c r="A7" s="7"/>
@@ -585,6 +620,9 @@
       <x:c r="S7" s="9"/>
       <x:c r="T7" s="8"/>
       <x:c r="U7" s="8"/>
+      <x:c r="V7" s="12"/>
+      <x:c r="W7" s="12"/>
+      <x:c r="X7" s="12"/>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="7"/>
@@ -608,6 +646,9 @@
       <x:c r="S8" s="9"/>
       <x:c r="T8" s="8"/>
       <x:c r="U8" s="8"/>
+      <x:c r="V8" s="12"/>
+      <x:c r="W8" s="12"/>
+      <x:c r="X8" s="12"/>
     </x:row>
     <x:row r="9" ht="23" customHeight="1">
       <x:c r="A9" s="7"/>
@@ -631,6 +672,9 @@
       <x:c r="S9" s="9"/>
       <x:c r="T9" s="8"/>
       <x:c r="U9" s="8"/>
+      <x:c r="V9" s="12"/>
+      <x:c r="W9" s="12"/>
+      <x:c r="X9" s="12"/>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
       <x:c r="A10" s="7"/>
@@ -654,6 +698,9 @@
       <x:c r="S10" s="9"/>
       <x:c r="T10" s="8"/>
       <x:c r="U10" s="8"/>
+      <x:c r="V10" s="12"/>
+      <x:c r="W10" s="12"/>
+      <x:c r="X10" s="12"/>
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
       <x:c r="A11" s="7"/>
@@ -677,6 +724,9 @@
       <x:c r="S11" s="9"/>
       <x:c r="T11" s="8"/>
       <x:c r="U11" s="8"/>
+      <x:c r="V11" s="12"/>
+      <x:c r="W11" s="12"/>
+      <x:c r="X11" s="12"/>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
       <x:c r="A12" s="7"/>
@@ -700,6 +750,9 @@
       <x:c r="S12" s="9"/>
       <x:c r="T12" s="8"/>
       <x:c r="U12" s="8"/>
+      <x:c r="V12" s="12"/>
+      <x:c r="W12" s="12"/>
+      <x:c r="X12" s="12"/>
     </x:row>
     <x:row r="13" ht="23" customHeight="1">
       <x:c r="A13" s="7"/>
@@ -723,6 +776,9 @@
       <x:c r="S13" s="9"/>
       <x:c r="T13" s="8"/>
       <x:c r="U13" s="8"/>
+      <x:c r="V13" s="12"/>
+      <x:c r="W13" s="12"/>
+      <x:c r="X13" s="12"/>
     </x:row>
     <x:row r="14" ht="23" customHeight="1">
       <x:c r="A14" s="7"/>
@@ -746,6 +802,9 @@
       <x:c r="S14" s="9"/>
       <x:c r="T14" s="8"/>
       <x:c r="U14" s="8"/>
+      <x:c r="V14" s="12"/>
+      <x:c r="W14" s="12"/>
+      <x:c r="X14" s="12"/>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
       <x:c r="A15" s="7"/>
@@ -769,6 +828,9 @@
       <x:c r="S15" s="9"/>
       <x:c r="T15" s="8"/>
       <x:c r="U15" s="8"/>
+      <x:c r="V15" s="12"/>
+      <x:c r="W15" s="12"/>
+      <x:c r="X15" s="12"/>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
       <x:c r="A16" s="7"/>
@@ -792,6 +854,9 @@
       <x:c r="S16" s="9"/>
       <x:c r="T16" s="8"/>
       <x:c r="U16" s="8"/>
+      <x:c r="V16" s="12"/>
+      <x:c r="W16" s="12"/>
+      <x:c r="X16" s="12"/>
     </x:row>
     <x:row r="17" ht="23" customHeight="1">
       <x:c r="A17" s="7"/>
@@ -815,6 +880,9 @@
       <x:c r="S17" s="9"/>
       <x:c r="T17" s="8"/>
       <x:c r="U17" s="8"/>
+      <x:c r="V17" s="12"/>
+      <x:c r="W17" s="12"/>
+      <x:c r="X17" s="12"/>
     </x:row>
     <x:row r="18" ht="23" customHeight="1">
       <x:c r="A18" s="7"/>
@@ -838,6 +906,9 @@
       <x:c r="S18" s="9"/>
       <x:c r="T18" s="8"/>
       <x:c r="U18" s="8"/>
+      <x:c r="V18" s="12"/>
+      <x:c r="W18" s="12"/>
+      <x:c r="X18" s="12"/>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
       <x:c r="A19" s="7"/>
@@ -861,6 +932,9 @@
       <x:c r="S19" s="9"/>
       <x:c r="T19" s="8"/>
       <x:c r="U19" s="8"/>
+      <x:c r="V19" s="12"/>
+      <x:c r="W19" s="12"/>
+      <x:c r="X19" s="12"/>
     </x:row>
     <x:row r="20" ht="23" customHeight="1">
       <x:c r="A20" s="7"/>
@@ -884,6 +958,9 @@
       <x:c r="S20" s="9"/>
       <x:c r="T20" s="8"/>
       <x:c r="U20" s="8"/>
+      <x:c r="V20" s="12"/>
+      <x:c r="W20" s="12"/>
+      <x:c r="X20" s="12"/>
     </x:row>
     <x:row r="21" ht="23" customHeight="1">
       <x:c r="A21" s="7"/>
@@ -907,6 +984,9 @@
       <x:c r="S21" s="9"/>
       <x:c r="T21" s="8"/>
       <x:c r="U21" s="8"/>
+      <x:c r="V21" s="12"/>
+      <x:c r="W21" s="12"/>
+      <x:c r="X21" s="12"/>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
       <x:c r="A22" s="7"/>
@@ -930,6 +1010,9 @@
       <x:c r="S22" s="9"/>
       <x:c r="T22" s="8"/>
       <x:c r="U22" s="8"/>
+      <x:c r="V22" s="12"/>
+      <x:c r="W22" s="12"/>
+      <x:c r="X22" s="12"/>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="7"/>
@@ -953,6 +1036,9 @@
       <x:c r="S23" s="9"/>
       <x:c r="T23" s="8"/>
       <x:c r="U23" s="8"/>
+      <x:c r="V23" s="12"/>
+      <x:c r="W23" s="12"/>
+      <x:c r="X23" s="12"/>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
       <x:c r="A24" s="7"/>
@@ -976,6 +1062,9 @@
       <x:c r="S24" s="9"/>
       <x:c r="T24" s="8"/>
       <x:c r="U24" s="8"/>
+      <x:c r="V24" s="12"/>
+      <x:c r="W24" s="12"/>
+      <x:c r="X24" s="12"/>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
       <x:c r="A25" s="7"/>
@@ -999,6 +1088,9 @@
       <x:c r="S25" s="9"/>
       <x:c r="T25" s="8"/>
       <x:c r="U25" s="8"/>
+      <x:c r="V25" s="12"/>
+      <x:c r="W25" s="12"/>
+      <x:c r="X25" s="12"/>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
       <x:c r="A26" s="7"/>
@@ -1022,6 +1114,9 @@
       <x:c r="S26" s="9"/>
       <x:c r="T26" s="8"/>
       <x:c r="U26" s="8"/>
+      <x:c r="V26" s="12"/>
+      <x:c r="W26" s="12"/>
+      <x:c r="X26" s="12"/>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
       <x:c r="A27" s="7"/>
@@ -1045,6 +1140,9 @@
       <x:c r="S27" s="9"/>
       <x:c r="T27" s="8"/>
       <x:c r="U27" s="8"/>
+      <x:c r="V27" s="12"/>
+      <x:c r="W27" s="12"/>
+      <x:c r="X27" s="12"/>
     </x:row>
     <x:row r="28" ht="23" customHeight="1">
       <x:c r="A28" s="7"/>
@@ -1068,6 +1166,9 @@
       <x:c r="S28" s="9"/>
       <x:c r="T28" s="8"/>
       <x:c r="U28" s="8"/>
+      <x:c r="V28" s="12"/>
+      <x:c r="W28" s="12"/>
+      <x:c r="X28" s="12"/>
     </x:row>
     <x:row r="29" ht="23" customHeight="1">
       <x:c r="A29" s="7"/>
@@ -1091,6 +1192,9 @@
       <x:c r="S29" s="9"/>
       <x:c r="T29" s="8"/>
       <x:c r="U29" s="8"/>
+      <x:c r="V29" s="12"/>
+      <x:c r="W29" s="12"/>
+      <x:c r="X29" s="12"/>
     </x:row>
     <x:row r="30" ht="23" customHeight="1">
       <x:c r="A30" s="7"/>
@@ -1114,6 +1218,9 @@
       <x:c r="S30" s="9"/>
       <x:c r="T30" s="8"/>
       <x:c r="U30" s="8"/>
+      <x:c r="V30" s="12"/>
+      <x:c r="W30" s="12"/>
+      <x:c r="X30" s="12"/>
     </x:row>
     <x:row r="31" ht="23" customHeight="1">
       <x:c r="A31" s="7"/>
@@ -1137,6 +1244,9 @@
       <x:c r="S31" s="9"/>
       <x:c r="T31" s="8"/>
       <x:c r="U31" s="8"/>
+      <x:c r="V31" s="12"/>
+      <x:c r="W31" s="12"/>
+      <x:c r="X31" s="12"/>
     </x:row>
     <x:row r="32" ht="23" customHeight="1">
       <x:c r="A32" s="7"/>
@@ -1160,6 +1270,9 @@
       <x:c r="S32" s="9"/>
       <x:c r="T32" s="8"/>
       <x:c r="U32" s="8"/>
+      <x:c r="V32" s="12"/>
+      <x:c r="W32" s="12"/>
+      <x:c r="X32" s="12"/>
     </x:row>
     <x:row r="33" ht="23" customHeight="1">
       <x:c r="A33" s="7"/>
@@ -1183,6 +1296,9 @@
       <x:c r="S33" s="9"/>
       <x:c r="T33" s="8"/>
       <x:c r="U33" s="8"/>
+      <x:c r="V33" s="12"/>
+      <x:c r="W33" s="12"/>
+      <x:c r="X33" s="12"/>
     </x:row>
     <x:row r="34" ht="23" customHeight="1">
       <x:c r="A34" s="7"/>
@@ -1206,6 +1322,9 @@
       <x:c r="S34" s="9"/>
       <x:c r="T34" s="8"/>
       <x:c r="U34" s="8"/>
+      <x:c r="V34" s="12"/>
+      <x:c r="W34" s="12"/>
+      <x:c r="X34" s="12"/>
     </x:row>
     <x:row r="35" ht="23" customHeight="1">
       <x:c r="A35" s="7"/>
@@ -1229,6 +1348,9 @@
       <x:c r="S35" s="9"/>
       <x:c r="T35" s="8"/>
       <x:c r="U35" s="8"/>
+      <x:c r="V35" s="12"/>
+      <x:c r="W35" s="12"/>
+      <x:c r="X35" s="12"/>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
       <x:c r="A36" s="7"/>
@@ -1252,6 +1374,9 @@
       <x:c r="S36" s="9"/>
       <x:c r="T36" s="8"/>
       <x:c r="U36" s="8"/>
+      <x:c r="V36" s="12"/>
+      <x:c r="W36" s="12"/>
+      <x:c r="X36" s="12"/>
     </x:row>
     <x:row r="37" ht="23" customHeight="1">
       <x:c r="A37" s="7"/>
@@ -1275,6 +1400,9 @@
       <x:c r="S37" s="9"/>
       <x:c r="T37" s="8"/>
       <x:c r="U37" s="8"/>
+      <x:c r="V37" s="12"/>
+      <x:c r="W37" s="12"/>
+      <x:c r="X37" s="12"/>
     </x:row>
     <x:row r="38" ht="23" customHeight="1">
       <x:c r="A38" s="7"/>
@@ -1298,6 +1426,9 @@
       <x:c r="S38" s="9"/>
       <x:c r="T38" s="8"/>
       <x:c r="U38" s="8"/>
+      <x:c r="V38" s="12"/>
+      <x:c r="W38" s="12"/>
+      <x:c r="X38" s="12"/>
     </x:row>
     <x:row r="39" ht="23" customHeight="1">
       <x:c r="A39" s="7"/>
@@ -1321,6 +1452,9 @@
       <x:c r="S39" s="9"/>
       <x:c r="T39" s="8"/>
       <x:c r="U39" s="8"/>
+      <x:c r="V39" s="12"/>
+      <x:c r="W39" s="12"/>
+      <x:c r="X39" s="12"/>
     </x:row>
     <x:row r="40" ht="23" customHeight="1">
       <x:c r="A40" s="7"/>
@@ -1344,6 +1478,9 @@
       <x:c r="S40" s="9"/>
       <x:c r="T40" s="8"/>
       <x:c r="U40" s="8"/>
+      <x:c r="V40" s="12"/>
+      <x:c r="W40" s="12"/>
+      <x:c r="X40" s="12"/>
     </x:row>
     <x:row r="41" ht="23" customHeight="1">
       <x:c r="A41" s="7"/>
@@ -1367,6 +1504,9 @@
       <x:c r="S41" s="9"/>
       <x:c r="T41" s="8"/>
       <x:c r="U41" s="8"/>
+      <x:c r="V41" s="12"/>
+      <x:c r="W41" s="12"/>
+      <x:c r="X41" s="12"/>
     </x:row>
     <x:row r="42" ht="23" customHeight="1">
       <x:c r="A42" s="7"/>
@@ -1390,6 +1530,9 @@
       <x:c r="S42" s="9"/>
       <x:c r="T42" s="8"/>
       <x:c r="U42" s="8"/>
+      <x:c r="V42" s="12"/>
+      <x:c r="W42" s="12"/>
+      <x:c r="X42" s="12"/>
     </x:row>
     <x:row r="43" ht="23" customHeight="1">
       <x:c r="A43" s="7"/>
@@ -1413,6 +1556,9 @@
       <x:c r="S43" s="9"/>
       <x:c r="T43" s="8"/>
       <x:c r="U43" s="8"/>
+      <x:c r="V43" s="12"/>
+      <x:c r="W43" s="12"/>
+      <x:c r="X43" s="12"/>
     </x:row>
     <x:row r="44" ht="23" customHeight="1">
       <x:c r="A44" s="7"/>
@@ -1436,6 +1582,9 @@
       <x:c r="S44" s="9"/>
       <x:c r="T44" s="8"/>
       <x:c r="U44" s="8"/>
+      <x:c r="V44" s="12"/>
+      <x:c r="W44" s="12"/>
+      <x:c r="X44" s="12"/>
     </x:row>
     <x:row r="45" ht="23" customHeight="1">
       <x:c r="A45" s="7"/>
@@ -1459,6 +1608,9 @@
       <x:c r="S45" s="9"/>
       <x:c r="T45" s="8"/>
       <x:c r="U45" s="8"/>
+      <x:c r="V45" s="12"/>
+      <x:c r="W45" s="12"/>
+      <x:c r="X45" s="12"/>
     </x:row>
     <x:row r="46" ht="23" customHeight="1">
       <x:c r="A46" s="7"/>
@@ -1482,6 +1634,9 @@
       <x:c r="S46" s="9"/>
       <x:c r="T46" s="8"/>
       <x:c r="U46" s="8"/>
+      <x:c r="V46" s="12"/>
+      <x:c r="W46" s="12"/>
+      <x:c r="X46" s="12"/>
     </x:row>
     <x:row r="47" ht="23" customHeight="1">
       <x:c r="A47" s="7"/>
@@ -1505,6 +1660,9 @@
       <x:c r="S47" s="9"/>
       <x:c r="T47" s="8"/>
       <x:c r="U47" s="8"/>
+      <x:c r="V47" s="12"/>
+      <x:c r="W47" s="12"/>
+      <x:c r="X47" s="12"/>
     </x:row>
     <x:row r="48" ht="23" customHeight="1">
       <x:c r="A48" s="7"/>
@@ -1528,6 +1686,9 @@
       <x:c r="S48" s="9"/>
       <x:c r="T48" s="8"/>
       <x:c r="U48" s="8"/>
+      <x:c r="V48" s="12"/>
+      <x:c r="W48" s="12"/>
+      <x:c r="X48" s="12"/>
     </x:row>
     <x:row r="49" ht="23" customHeight="1">
       <x:c r="A49" s="7"/>
@@ -1551,6 +1712,9 @@
       <x:c r="S49" s="9"/>
       <x:c r="T49" s="8"/>
       <x:c r="U49" s="8"/>
+      <x:c r="V49" s="12"/>
+      <x:c r="W49" s="12"/>
+      <x:c r="X49" s="12"/>
     </x:row>
     <x:row r="50" ht="23" customHeight="1">
       <x:c r="A50" s="7"/>
@@ -1574,6 +1738,9 @@
       <x:c r="S50" s="9"/>
       <x:c r="T50" s="8"/>
       <x:c r="U50" s="8"/>
+      <x:c r="V50" s="12"/>
+      <x:c r="W50" s="12"/>
+      <x:c r="X50" s="12"/>
     </x:row>
     <x:row r="51" ht="23" customHeight="1">
       <x:c r="A51" s="7"/>
@@ -1597,6 +1764,9 @@
       <x:c r="S51" s="9"/>
       <x:c r="T51" s="8"/>
       <x:c r="U51" s="8"/>
+      <x:c r="V51" s="12"/>
+      <x:c r="W51" s="12"/>
+      <x:c r="X51" s="12"/>
     </x:row>
     <x:row r="52" ht="23" customHeight="1">
       <x:c r="A52" s="7"/>
@@ -1620,6 +1790,9 @@
       <x:c r="S52" s="9"/>
       <x:c r="T52" s="8"/>
       <x:c r="U52" s="8"/>
+      <x:c r="V52" s="12"/>
+      <x:c r="W52" s="12"/>
+      <x:c r="X52" s="12"/>
     </x:row>
     <x:row r="53" ht="23" customHeight="1">
       <x:c r="A53" s="7"/>
@@ -1643,6 +1816,9 @@
       <x:c r="S53" s="9"/>
       <x:c r="T53" s="8"/>
       <x:c r="U53" s="8"/>
+      <x:c r="V53" s="12"/>
+      <x:c r="W53" s="12"/>
+      <x:c r="X53" s="12"/>
     </x:row>
     <x:row r="54" ht="23" customHeight="1">
       <x:c r="A54" s="7"/>
@@ -1666,6 +1842,9 @@
       <x:c r="S54" s="9"/>
       <x:c r="T54" s="8"/>
       <x:c r="U54" s="8"/>
+      <x:c r="V54" s="12"/>
+      <x:c r="W54" s="12"/>
+      <x:c r="X54" s="12"/>
     </x:row>
     <x:row r="55" ht="23" customHeight="1">
       <x:c r="A55" s="7"/>
@@ -1689,6 +1868,9 @@
       <x:c r="S55" s="9"/>
       <x:c r="T55" s="8"/>
       <x:c r="U55" s="8"/>
+      <x:c r="V55" s="12"/>
+      <x:c r="W55" s="12"/>
+      <x:c r="X55" s="12"/>
     </x:row>
     <x:row r="56" ht="23" customHeight="1">
       <x:c r="A56" s="7"/>
@@ -1712,6 +1894,9 @@
       <x:c r="S56" s="9"/>
       <x:c r="T56" s="8"/>
       <x:c r="U56" s="8"/>
+      <x:c r="V56" s="12"/>
+      <x:c r="W56" s="12"/>
+      <x:c r="X56" s="12"/>
     </x:row>
     <x:row r="57" ht="23" customHeight="1">
       <x:c r="A57" s="7"/>
@@ -1735,6 +1920,9 @@
       <x:c r="S57" s="9"/>
       <x:c r="T57" s="8"/>
       <x:c r="U57" s="8"/>
+      <x:c r="V57" s="12"/>
+      <x:c r="W57" s="12"/>
+      <x:c r="X57" s="12"/>
     </x:row>
     <x:row r="58" ht="23" customHeight="1">
       <x:c r="A58" s="7"/>
@@ -1758,6 +1946,9 @@
       <x:c r="S58" s="9"/>
       <x:c r="T58" s="8"/>
       <x:c r="U58" s="8"/>
+      <x:c r="V58" s="12"/>
+      <x:c r="W58" s="12"/>
+      <x:c r="X58" s="12"/>
     </x:row>
     <x:row r="59" ht="23" customHeight="1">
       <x:c r="A59" s="7"/>
@@ -1781,6 +1972,9 @@
       <x:c r="S59" s="9"/>
       <x:c r="T59" s="8"/>
       <x:c r="U59" s="8"/>
+      <x:c r="V59" s="12"/>
+      <x:c r="W59" s="12"/>
+      <x:c r="X59" s="12"/>
     </x:row>
     <x:row r="60" ht="23" customHeight="1">
       <x:c r="A60" s="7"/>
@@ -1804,6 +1998,9 @@
       <x:c r="S60" s="9"/>
       <x:c r="T60" s="8"/>
       <x:c r="U60" s="8"/>
+      <x:c r="V60" s="12"/>
+      <x:c r="W60" s="12"/>
+      <x:c r="X60" s="12"/>
     </x:row>
     <x:row r="61" ht="23" customHeight="1">
       <x:c r="A61" s="7"/>
@@ -1827,6 +2024,9 @@
       <x:c r="S61" s="9"/>
       <x:c r="T61" s="8"/>
       <x:c r="U61" s="8"/>
+      <x:c r="V61" s="12"/>
+      <x:c r="W61" s="12"/>
+      <x:c r="X61" s="12"/>
     </x:row>
     <x:row r="62" ht="23" customHeight="1">
       <x:c r="A62" s="7"/>
@@ -1850,6 +2050,9 @@
       <x:c r="S62" s="9"/>
       <x:c r="T62" s="8"/>
       <x:c r="U62" s="8"/>
+      <x:c r="V62" s="12"/>
+      <x:c r="W62" s="12"/>
+      <x:c r="X62" s="12"/>
     </x:row>
     <x:row r="63" ht="23" customHeight="1">
       <x:c r="A63" s="7"/>
@@ -1873,6 +2076,9 @@
       <x:c r="S63" s="9"/>
       <x:c r="T63" s="8"/>
       <x:c r="U63" s="8"/>
+      <x:c r="V63" s="12"/>
+      <x:c r="W63" s="12"/>
+      <x:c r="X63" s="12"/>
     </x:row>
     <x:row r="64" ht="23" customHeight="1">
       <x:c r="A64" s="7"/>
@@ -1896,6 +2102,9 @@
       <x:c r="S64" s="9"/>
       <x:c r="T64" s="8"/>
       <x:c r="U64" s="8"/>
+      <x:c r="V64" s="12"/>
+      <x:c r="W64" s="12"/>
+      <x:c r="X64" s="12"/>
     </x:row>
     <x:row r="65" ht="23" customHeight="1">
       <x:c r="A65" s="7"/>
@@ -1919,6 +2128,9 @@
       <x:c r="S65" s="9"/>
       <x:c r="T65" s="8"/>
       <x:c r="U65" s="8"/>
+      <x:c r="V65" s="12"/>
+      <x:c r="W65" s="12"/>
+      <x:c r="X65" s="12"/>
     </x:row>
     <x:row r="66" ht="23" customHeight="1">
       <x:c r="A66" s="7"/>
@@ -1942,6 +2154,9 @@
       <x:c r="S66" s="9"/>
       <x:c r="T66" s="8"/>
       <x:c r="U66" s="8"/>
+      <x:c r="V66" s="12"/>
+      <x:c r="W66" s="12"/>
+      <x:c r="X66" s="12"/>
     </x:row>
     <x:row r="67" ht="23" customHeight="1">
       <x:c r="A67" s="7"/>
@@ -1965,6 +2180,9 @@
       <x:c r="S67" s="9"/>
       <x:c r="T67" s="8"/>
       <x:c r="U67" s="8"/>
+      <x:c r="V67" s="12"/>
+      <x:c r="W67" s="12"/>
+      <x:c r="X67" s="12"/>
     </x:row>
     <x:row r="68" ht="23" customHeight="1">
       <x:c r="A68" s="7"/>
@@ -1988,6 +2206,9 @@
       <x:c r="S68" s="9"/>
       <x:c r="T68" s="8"/>
       <x:c r="U68" s="8"/>
+      <x:c r="V68" s="12"/>
+      <x:c r="W68" s="12"/>
+      <x:c r="X68" s="12"/>
     </x:row>
     <x:row r="69" ht="23" customHeight="1">
       <x:c r="A69" s="7"/>
@@ -2011,6 +2232,9 @@
       <x:c r="S69" s="9"/>
       <x:c r="T69" s="8"/>
       <x:c r="U69" s="8"/>
+      <x:c r="V69" s="12"/>
+      <x:c r="W69" s="12"/>
+      <x:c r="X69" s="12"/>
     </x:row>
     <x:row r="70" ht="23" customHeight="1">
       <x:c r="A70" s="7"/>
@@ -2034,6 +2258,9 @@
       <x:c r="S70" s="9"/>
       <x:c r="T70" s="8"/>
       <x:c r="U70" s="8"/>
+      <x:c r="V70" s="12"/>
+      <x:c r="W70" s="12"/>
+      <x:c r="X70" s="12"/>
     </x:row>
     <x:row r="71" ht="23" customHeight="1">
       <x:c r="A71" s="7"/>
@@ -2057,6 +2284,9 @@
       <x:c r="S71" s="9"/>
       <x:c r="T71" s="8"/>
       <x:c r="U71" s="8"/>
+      <x:c r="V71" s="12"/>
+      <x:c r="W71" s="12"/>
+      <x:c r="X71" s="12"/>
     </x:row>
     <x:row r="72" ht="23" customHeight="1">
       <x:c r="A72" s="7"/>
@@ -2080,6 +2310,9 @@
       <x:c r="S72" s="9"/>
       <x:c r="T72" s="8"/>
       <x:c r="U72" s="8"/>
+      <x:c r="V72" s="12"/>
+      <x:c r="W72" s="12"/>
+      <x:c r="X72" s="12"/>
     </x:row>
     <x:row r="73" ht="23" customHeight="1">
       <x:c r="A73" s="7"/>
@@ -2103,6 +2336,9 @@
       <x:c r="S73" s="9"/>
       <x:c r="T73" s="8"/>
       <x:c r="U73" s="8"/>
+      <x:c r="V73" s="12"/>
+      <x:c r="W73" s="12"/>
+      <x:c r="X73" s="12"/>
     </x:row>
     <x:row r="74" ht="23" customHeight="1">
       <x:c r="A74" s="7"/>
@@ -2126,6 +2362,9 @@
       <x:c r="S74" s="9"/>
       <x:c r="T74" s="8"/>
       <x:c r="U74" s="8"/>
+      <x:c r="V74" s="12"/>
+      <x:c r="W74" s="12"/>
+      <x:c r="X74" s="12"/>
     </x:row>
     <x:row r="75" ht="23" customHeight="1">
       <x:c r="A75" s="7"/>
@@ -2149,6 +2388,9 @@
       <x:c r="S75" s="9"/>
       <x:c r="T75" s="8"/>
       <x:c r="U75" s="8"/>
+      <x:c r="V75" s="12"/>
+      <x:c r="W75" s="12"/>
+      <x:c r="X75" s="12"/>
     </x:row>
     <x:row r="76" ht="23" customHeight="1">
       <x:c r="A76" s="7"/>
@@ -2172,6 +2414,9 @@
       <x:c r="S76" s="9"/>
       <x:c r="T76" s="8"/>
       <x:c r="U76" s="8"/>
+      <x:c r="V76" s="12"/>
+      <x:c r="W76" s="12"/>
+      <x:c r="X76" s="12"/>
     </x:row>
     <x:row r="77" ht="23" customHeight="1">
       <x:c r="A77" s="7"/>
@@ -2195,6 +2440,9 @@
       <x:c r="S77" s="9"/>
       <x:c r="T77" s="8"/>
       <x:c r="U77" s="8"/>
+      <x:c r="V77" s="12"/>
+      <x:c r="W77" s="12"/>
+      <x:c r="X77" s="12"/>
     </x:row>
     <x:row r="78" ht="23" customHeight="1">
       <x:c r="A78" s="7"/>
@@ -2218,6 +2466,9 @@
       <x:c r="S78" s="9"/>
       <x:c r="T78" s="8"/>
       <x:c r="U78" s="8"/>
+      <x:c r="V78" s="12"/>
+      <x:c r="W78" s="12"/>
+      <x:c r="X78" s="12"/>
     </x:row>
     <x:row r="79" ht="23" customHeight="1">
       <x:c r="A79" s="7"/>
@@ -2241,6 +2492,9 @@
       <x:c r="S79" s="9"/>
       <x:c r="T79" s="8"/>
       <x:c r="U79" s="8"/>
+      <x:c r="V79" s="12"/>
+      <x:c r="W79" s="12"/>
+      <x:c r="X79" s="12"/>
     </x:row>
     <x:row r="80" ht="23" customHeight="1">
       <x:c r="A80" s="7"/>
@@ -2264,6 +2518,9 @@
       <x:c r="S80" s="9"/>
       <x:c r="T80" s="8"/>
       <x:c r="U80" s="8"/>
+      <x:c r="V80" s="12"/>
+      <x:c r="W80" s="12"/>
+      <x:c r="X80" s="12"/>
     </x:row>
     <x:row r="81" ht="23" customHeight="1">
       <x:c r="A81" s="7"/>
@@ -2287,6 +2544,9 @@
       <x:c r="S81" s="9"/>
       <x:c r="T81" s="8"/>
       <x:c r="U81" s="8"/>
+      <x:c r="V81" s="12"/>
+      <x:c r="W81" s="12"/>
+      <x:c r="X81" s="12"/>
     </x:row>
     <x:row r="82" ht="23" customHeight="1">
       <x:c r="A82" s="7"/>
@@ -2310,6 +2570,9 @@
       <x:c r="S82" s="9"/>
       <x:c r="T82" s="8"/>
       <x:c r="U82" s="8"/>
+      <x:c r="V82" s="12"/>
+      <x:c r="W82" s="12"/>
+      <x:c r="X82" s="12"/>
     </x:row>
     <x:row r="83" ht="23" customHeight="1">
       <x:c r="A83" s="7"/>
@@ -2333,6 +2596,9 @@
       <x:c r="S83" s="9"/>
       <x:c r="T83" s="8"/>
       <x:c r="U83" s="8"/>
+      <x:c r="V83" s="12"/>
+      <x:c r="W83" s="12"/>
+      <x:c r="X83" s="12"/>
     </x:row>
     <x:row r="84" ht="23" customHeight="1">
       <x:c r="A84" s="7"/>
@@ -2356,6 +2622,9 @@
       <x:c r="S84" s="9"/>
       <x:c r="T84" s="8"/>
       <x:c r="U84" s="8"/>
+      <x:c r="V84" s="12"/>
+      <x:c r="W84" s="12"/>
+      <x:c r="X84" s="12"/>
     </x:row>
     <x:row r="85" ht="23" customHeight="1">
       <x:c r="A85" s="7"/>
@@ -2379,6 +2648,9 @@
       <x:c r="S85" s="9"/>
       <x:c r="T85" s="8"/>
       <x:c r="U85" s="8"/>
+      <x:c r="V85" s="12"/>
+      <x:c r="W85" s="12"/>
+      <x:c r="X85" s="12"/>
     </x:row>
     <x:row r="86" ht="23" customHeight="1">
       <x:c r="A86" s="7"/>
@@ -2402,6 +2674,9 @@
       <x:c r="S86" s="9"/>
       <x:c r="T86" s="8"/>
       <x:c r="U86" s="8"/>
+      <x:c r="V86" s="12"/>
+      <x:c r="W86" s="12"/>
+      <x:c r="X86" s="12"/>
     </x:row>
     <x:row r="87" ht="23" customHeight="1">
       <x:c r="A87" s="7"/>
@@ -2425,6 +2700,9 @@
       <x:c r="S87" s="9"/>
       <x:c r="T87" s="8"/>
       <x:c r="U87" s="8"/>
+      <x:c r="V87" s="12"/>
+      <x:c r="W87" s="12"/>
+      <x:c r="X87" s="12"/>
     </x:row>
     <x:row r="88" ht="23" customHeight="1">
       <x:c r="A88" s="7"/>
@@ -2448,6 +2726,9 @@
       <x:c r="S88" s="9"/>
       <x:c r="T88" s="8"/>
       <x:c r="U88" s="8"/>
+      <x:c r="V88" s="12"/>
+      <x:c r="W88" s="12"/>
+      <x:c r="X88" s="12"/>
     </x:row>
     <x:row r="89" ht="23" customHeight="1">
       <x:c r="A89" s="7"/>
@@ -2471,6 +2752,9 @@
       <x:c r="S89" s="9"/>
       <x:c r="T89" s="8"/>
       <x:c r="U89" s="8"/>
+      <x:c r="V89" s="12"/>
+      <x:c r="W89" s="12"/>
+      <x:c r="X89" s="12"/>
     </x:row>
     <x:row r="90" ht="23" customHeight="1">
       <x:c r="A90" s="7"/>
@@ -2494,6 +2778,9 @@
       <x:c r="S90" s="9"/>
       <x:c r="T90" s="8"/>
       <x:c r="U90" s="8"/>
+      <x:c r="V90" s="12"/>
+      <x:c r="W90" s="12"/>
+      <x:c r="X90" s="12"/>
     </x:row>
     <x:row r="91" ht="23" customHeight="1">
       <x:c r="A91" s="7"/>
@@ -2517,6 +2804,9 @@
       <x:c r="S91" s="9"/>
       <x:c r="T91" s="8"/>
       <x:c r="U91" s="8"/>
+      <x:c r="V91" s="12"/>
+      <x:c r="W91" s="12"/>
+      <x:c r="X91" s="12"/>
     </x:row>
     <x:row r="92" ht="23" customHeight="1">
       <x:c r="A92" s="7"/>
@@ -2540,6 +2830,9 @@
       <x:c r="S92" s="9"/>
       <x:c r="T92" s="8"/>
       <x:c r="U92" s="8"/>
+      <x:c r="V92" s="12"/>
+      <x:c r="W92" s="12"/>
+      <x:c r="X92" s="12"/>
     </x:row>
     <x:row r="93" ht="23" customHeight="1">
       <x:c r="A93" s="7"/>
@@ -2563,6 +2856,9 @@
       <x:c r="S93" s="9"/>
       <x:c r="T93" s="8"/>
       <x:c r="U93" s="8"/>
+      <x:c r="V93" s="12"/>
+      <x:c r="W93" s="12"/>
+      <x:c r="X93" s="12"/>
     </x:row>
     <x:row r="94" ht="23" customHeight="1">
       <x:c r="A94" s="7"/>
@@ -2586,6 +2882,9 @@
       <x:c r="S94" s="9"/>
       <x:c r="T94" s="8"/>
       <x:c r="U94" s="8"/>
+      <x:c r="V94" s="12"/>
+      <x:c r="W94" s="12"/>
+      <x:c r="X94" s="12"/>
     </x:row>
     <x:row r="95" ht="23" customHeight="1">
       <x:c r="A95" s="7"/>
@@ -2609,6 +2908,9 @@
       <x:c r="S95" s="9"/>
       <x:c r="T95" s="8"/>
       <x:c r="U95" s="8"/>
+      <x:c r="V95" s="12"/>
+      <x:c r="W95" s="12"/>
+      <x:c r="X95" s="12"/>
     </x:row>
     <x:row r="96" ht="23" customHeight="1">
       <x:c r="A96" s="7"/>
@@ -2632,6 +2934,9 @@
       <x:c r="S96" s="9"/>
       <x:c r="T96" s="8"/>
       <x:c r="U96" s="8"/>
+      <x:c r="V96" s="12"/>
+      <x:c r="W96" s="12"/>
+      <x:c r="X96" s="12"/>
     </x:row>
     <x:row r="97" ht="23" customHeight="1">
       <x:c r="A97" s="7"/>
@@ -2655,6 +2960,9 @@
       <x:c r="S97" s="9"/>
       <x:c r="T97" s="8"/>
       <x:c r="U97" s="8"/>
+      <x:c r="V97" s="12"/>
+      <x:c r="W97" s="12"/>
+      <x:c r="X97" s="12"/>
     </x:row>
     <x:row r="98" ht="23" customHeight="1">
       <x:c r="A98" s="7"/>
@@ -2678,6 +2986,9 @@
       <x:c r="S98" s="9"/>
       <x:c r="T98" s="8"/>
       <x:c r="U98" s="8"/>
+      <x:c r="V98" s="12"/>
+      <x:c r="W98" s="12"/>
+      <x:c r="X98" s="12"/>
     </x:row>
     <x:row r="99" ht="23" customHeight="1">
       <x:c r="A99" s="7"/>
@@ -2701,6 +3012,9 @@
       <x:c r="S99" s="9"/>
       <x:c r="T99" s="8"/>
       <x:c r="U99" s="8"/>
+      <x:c r="V99" s="12"/>
+      <x:c r="W99" s="12"/>
+      <x:c r="X99" s="12"/>
     </x:row>
     <x:row r="100" ht="23" customHeight="1">
       <x:c r="A100" s="7"/>
@@ -2724,6 +3038,9 @@
       <x:c r="S100" s="9"/>
       <x:c r="T100" s="8"/>
       <x:c r="U100" s="8"/>
+      <x:c r="V100" s="12"/>
+      <x:c r="W100" s="12"/>
+      <x:c r="X100" s="12"/>
     </x:row>
     <x:row r="101" ht="23" customHeight="1">
       <x:c r="A101" s="7"/>
@@ -2747,11 +3064,14 @@
       <x:c r="S101" s="9"/>
       <x:c r="T101" s="8"/>
       <x:c r="U101" s="8"/>
+      <x:c r="V101" s="12"/>
+      <x:c r="W101" s="12"/>
+      <x:c r="X101" s="12"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ec606cd33d44fd6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c09fb087ece4cb2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2781,6 +3101,9 @@
     <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="18" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="23" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="23" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="23" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -2847,998 +3170,2511 @@
       <x:c r="U1" s="5" t="str">
         <x:v>Website traffic</x:v>
       </x:c>
+      <x:c r="V1" s="5" t="str">
+        <x:v>Platform</x:v>
+      </x:c>
+      <x:c r="W1" s="5" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="X1" s="5" t="str">
+        <x:v>Campaign ID</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="23" customHeight="1">
       <x:c r="A2" s="7" t="n">
-        <x:v>46265</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="str">
-        <x:v>Paid search</x:v>
-      </x:c>
-      <x:c r="C2" s="6" t="str">
-        <x:v>Brand search</x:v>
-      </x:c>
-      <x:c r="D2" s="6" t="str">
-        <x:v>Text A</x:v>
-      </x:c>
-      <x:c r="E2" s="6" t="str">
-        <x:v>UK</x:v>
-      </x:c>
-      <x:c r="F2" s="6" t="str">
-        <x:v>Subscription</x:v>
-      </x:c>
+        <x:v>46142</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Brand &amp; non-brand</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Search text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" s="6"/>
+      <x:c r="F2" s="6"/>
       <x:c r="G2" s="9" t="n">
-        <x:v>1200</x:v>
+        <x:v>12500</x:v>
       </x:c>
       <x:c r="H2" s="9" t="n">
-        <x:v>4800</x:v>
+        <x:v>46500</x:v>
       </x:c>
       <x:c r="I2" s="8" t="n">
-        <x:v>40000</x:v>
-      </x:c>
-      <x:c r="J2" s="8" t="n">
-        <x:v>28000</x:v>
-      </x:c>
+        <x:v>190000</x:v>
+      </x:c>
+      <x:c r="J2" s="8"/>
       <x:c r="K2" s="8" t="n">
-        <x:v>1200</x:v>
+        <x:v>8200</x:v>
       </x:c>
       <x:c r="L2" s="8" t="n">
-        <x:v>100</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="M2" s="8" t="n">
-        <x:v>65</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="N2" s="8" t="n">
-        <x:v>30</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="O2" s="8" t="n">
-        <x:v>20</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="P2" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="Q2" s="9" t="n">
-        <x:v>12000</x:v>
-      </x:c>
-      <x:c r="R2" s="9" t="n">
-        <x:v>2400</x:v>
-      </x:c>
-      <x:c r="S2" s="9" t="n">
-        <x:v>1500</x:v>
-      </x:c>
+        <x:v>83700</x:v>
+      </x:c>
+      <x:c r="R2" s="9"/>
+      <x:c r="S2" s="9"/>
       <x:c r="T2" s="8"/>
-      <x:c r="U2" s="8" t="n">
-        <x:v>2800</x:v>
+      <x:c r="U2" s="8"/>
+      <x:c r="V2" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Google Ads</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W2" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X2" s="12" t="inlineStr">
+        <x:is>
+          <x:t>GOOGLE-101</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="7" t="n">
-        <x:v>46265</x:v>
-      </x:c>
-      <x:c r="B3" s="6" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="C3" s="6" t="str">
-        <x:v>Lifecycle</x:v>
-      </x:c>
-      <x:c r="D3" s="6" t="str">
-        <x:v>Welcome email</x:v>
-      </x:c>
-      <x:c r="E3" s="6" t="str">
-        <x:v>UK</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="str">
-        <x:v>Subscription</x:v>
-      </x:c>
+        <x:v>46142</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Prospecting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Static image</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" s="6"/>
+      <x:c r="F3" s="6"/>
       <x:c r="G3" s="9" t="n">
-        <x:v>300</x:v>
+        <x:v>3480</x:v>
       </x:c>
       <x:c r="H3" s="9" t="n">
-        <x:v>1800</x:v>
+        <x:v>7680</x:v>
       </x:c>
       <x:c r="I3" s="8" t="n">
-        <x:v>10000</x:v>
-      </x:c>
-      <x:c r="J3" s="8" t="n">
-        <x:v>8000</x:v>
-      </x:c>
+        <x:v>216000</x:v>
+      </x:c>
+      <x:c r="J3" s="8"/>
       <x:c r="K3" s="8" t="n">
-        <x:v>500</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="L3" s="8" t="n">
-        <x:v>40</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="M3" s="8" t="n">
-        <x:v>25</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="N3" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O3" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P3" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="Q3" s="9" t="n">
-        <x:v>4500</x:v>
-      </x:c>
-      <x:c r="R3" s="9" t="n">
-        <x:v>900</x:v>
-      </x:c>
-      <x:c r="S3" s="9" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="T3" s="8" t="n">
-        <x:v>2100</x:v>
-      </x:c>
-      <x:c r="U3" s="8" t="n">
-        <x:v>700</x:v>
+        <x:v>13824</x:v>
+      </x:c>
+      <x:c r="R3" s="9"/>
+      <x:c r="S3" s="9"/>
+      <x:c r="T3" s="8"/>
+      <x:c r="U3" s="8"/>
+      <x:c r="V3" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Meta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W3" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Facebook</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X3" s="12" t="inlineStr">
+        <x:is>
+          <x:t>META-101</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="7" t="n">
-        <x:v>46295</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="str">
-        <x:v>Paid search</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="str">
-        <x:v>Brand search</x:v>
-      </x:c>
-      <x:c r="D4" s="6" t="str">
-        <x:v>Text A</x:v>
-      </x:c>
-      <x:c r="E4" s="6" t="str">
-        <x:v>UK</x:v>
-      </x:c>
-      <x:c r="F4" s="6" t="str">
-        <x:v>Subscription</x:v>
-      </x:c>
+        <x:v>46142</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Prospecting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Short video</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
       <x:c r="G4" s="9" t="n">
-        <x:v>1500</x:v>
+        <x:v>3045</x:v>
       </x:c>
       <x:c r="H4" s="9" t="n">
-        <x:v>6000</x:v>
+        <x:v>6720</x:v>
       </x:c>
       <x:c r="I4" s="8" t="n">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="J4" s="8" t="n">
-        <x:v>35000</x:v>
-      </x:c>
+        <x:v>189000</x:v>
+      </x:c>
+      <x:c r="J4" s="8"/>
       <x:c r="K4" s="8" t="n">
-        <x:v>1500</x:v>
+        <x:v>3325</x:v>
       </x:c>
       <x:c r="L4" s="8" t="n">
-        <x:v>120</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M4" s="8" t="n">
-        <x:v>80</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="N4" s="8" t="n">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="O4" s="8" t="n">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P4" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="Q4" s="9" t="n">
-        <x:v>15000</x:v>
-      </x:c>
-      <x:c r="R4" s="9" t="n">
-        <x:v>3000</x:v>
-      </x:c>
-      <x:c r="S4" s="9" t="n">
-        <x:v>1800</x:v>
-      </x:c>
+        <x:v>12096</x:v>
+      </x:c>
+      <x:c r="R4" s="9"/>
+      <x:c r="S4" s="9"/>
       <x:c r="T4" s="8"/>
-      <x:c r="U4" s="8" t="n">
-        <x:v>3500</x:v>
+      <x:c r="U4" s="8"/>
+      <x:c r="V4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Meta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Instagram</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>META-101</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
       <x:c r="A5" s="7" t="n">
-        <x:v>46295</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="str">
-        <x:v>Email</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="str">
-        <x:v>Lifecycle</x:v>
-      </x:c>
-      <x:c r="D5" s="6" t="str">
-        <x:v>Welcome email</x:v>
-      </x:c>
-      <x:c r="E5" s="6" t="str">
-        <x:v>UK</x:v>
-      </x:c>
-      <x:c r="F5" s="6" t="str">
-        <x:v>Subscription</x:v>
-      </x:c>
+        <x:v>46142</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Business leads</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Static image</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="6"/>
+      <x:c r="F5" s="6"/>
       <x:c r="G5" s="9" t="n">
-        <x:v>350</x:v>
+        <x:v>2175</x:v>
       </x:c>
       <x:c r="H5" s="9" t="n">
-        <x:v>2100</x:v>
+        <x:v>4800</x:v>
       </x:c>
       <x:c r="I5" s="8" t="n">
-        <x:v>12000</x:v>
-      </x:c>
-      <x:c r="J5" s="8" t="n">
-        <x:v>9500</x:v>
-      </x:c>
+        <x:v>135000</x:v>
+      </x:c>
+      <x:c r="J5" s="8"/>
       <x:c r="K5" s="8" t="n">
-        <x:v>600</x:v>
+        <x:v>2375</x:v>
       </x:c>
       <x:c r="L5" s="8" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="M5" s="8" t="n">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="N5" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O5" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="P5" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="Q5" s="9" t="n">
-        <x:v>5500</x:v>
-      </x:c>
-      <x:c r="R5" s="9" t="n">
-        <x:v>1050</x:v>
-      </x:c>
-      <x:c r="S5" s="9" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="T5" s="8" t="n">
-        <x:v>2500</x:v>
-      </x:c>
-      <x:c r="U5" s="8" t="n">
-        <x:v>850</x:v>
+        <x:v>8640</x:v>
+      </x:c>
+      <x:c r="R5" s="9"/>
+      <x:c r="S5" s="9"/>
+      <x:c r="T5" s="8"/>
+      <x:c r="U5" s="8"/>
+      <x:c r="V5" s="12" t="inlineStr">
+        <x:is>
+          <x:t>LinkedIn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W5" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Feed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X5" s="12" t="inlineStr">
+        <x:is>
+          <x:t>LI-101</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6" ht="23" customHeight="1">
-      <x:c r="A6" s="7"/>
-      <x:c r="B6" s="6"/>
-      <x:c r="C6" s="6"/>
+      <x:c r="A6" s="7" t="n">
+        <x:v>46142</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Email</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Lifecycle</x:t>
+        </x:is>
+      </x:c>
       <x:c r="D6" s="6"/>
       <x:c r="E6" s="6"/>
       <x:c r="F6" s="6"/>
-      <x:c r="G6" s="9"/>
-      <x:c r="H6" s="9"/>
-      <x:c r="I6" s="8"/>
+      <x:c r="G6" s="9" t="n">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="H6" s="9" t="n">
+        <x:v>20200</x:v>
+      </x:c>
+      <x:c r="I6" s="8" t="n">
+        <x:v>37000</x:v>
+      </x:c>
       <x:c r="J6" s="8"/>
-      <x:c r="K6" s="8"/>
-      <x:c r="L6" s="8"/>
-      <x:c r="M6" s="8"/>
-      <x:c r="N6" s="8"/>
-      <x:c r="O6" s="8"/>
-      <x:c r="P6" s="8"/>
-      <x:c r="Q6" s="9"/>
+      <x:c r="K6" s="8" t="n">
+        <x:v>5400</x:v>
+      </x:c>
+      <x:c r="L6" s="8" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="M6" s="8" t="n">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="N6" s="8" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="O6" s="8" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="P6" s="8" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="Q6" s="9" t="n">
+        <x:v>36360</x:v>
+      </x:c>
       <x:c r="R6" s="9"/>
       <x:c r="S6" s="9"/>
       <x:c r="T6" s="8"/>
       <x:c r="U6" s="8"/>
+      <x:c r="V6" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Email</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W6" s="12"/>
+      <x:c r="X6" s="12" t="inlineStr">
+        <x:is>
+          <x:t>EMAIL-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="7" ht="23" customHeight="1">
-      <x:c r="A7" s="7"/>
-      <x:c r="B7" s="6"/>
-      <x:c r="C7" s="6"/>
+      <x:c r="A7" s="7" t="n">
+        <x:v>46142</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Organic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Content</x:t>
+        </x:is>
+      </x:c>
       <x:c r="D7" s="6"/>
       <x:c r="E7" s="6"/>
       <x:c r="F7" s="6"/>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="9"/>
-      <x:c r="I7" s="8"/>
+      <x:c r="G7" s="9" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="H7" s="9" t="n">
+        <x:v>9600</x:v>
+      </x:c>
+      <x:c r="I7" s="8" t="n">
+        <x:v>98000</x:v>
+      </x:c>
       <x:c r="J7" s="8"/>
-      <x:c r="K7" s="8"/>
-      <x:c r="L7" s="8"/>
-      <x:c r="M7" s="8"/>
-      <x:c r="N7" s="8"/>
-      <x:c r="O7" s="8"/>
-      <x:c r="P7" s="8"/>
-      <x:c r="Q7" s="9"/>
+      <x:c r="K7" s="8" t="n">
+        <x:v>4200</x:v>
+      </x:c>
+      <x:c r="L7" s="8" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="M7" s="8" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="N7" s="8" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="O7" s="8" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="P7" s="8" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q7" s="9" t="n">
+        <x:v>17280</x:v>
+      </x:c>
       <x:c r="R7" s="9"/>
       <x:c r="S7" s="9"/>
       <x:c r="T7" s="8"/>
       <x:c r="U7" s="8"/>
+      <x:c r="V7" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Organic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W7" s="12"/>
+      <x:c r="X7" s="12" t="inlineStr">
+        <x:is>
+          <x:t>ORGANIC-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
-      <x:c r="A8" s="7"/>
-      <x:c r="B8" s="6"/>
-      <x:c r="C8" s="6"/>
-      <x:c r="D8" s="6"/>
+      <x:c r="A8" s="7" t="n">
+        <x:v>46173</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Brand &amp; non-brand</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Search text</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E8" s="6"/>
       <x:c r="F8" s="6"/>
-      <x:c r="G8" s="9"/>
-      <x:c r="H8" s="9"/>
-      <x:c r="I8" s="8"/>
+      <x:c r="G8" s="9" t="n">
+        <x:v>12937</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="n">
+        <x:v>50685</x:v>
+      </x:c>
+      <x:c r="I8" s="8" t="n">
+        <x:v>190000</x:v>
+      </x:c>
       <x:c r="J8" s="8"/>
-      <x:c r="K8" s="8"/>
-      <x:c r="L8" s="8"/>
-      <x:c r="M8" s="8"/>
-      <x:c r="N8" s="8"/>
-      <x:c r="O8" s="8"/>
-      <x:c r="P8" s="8"/>
-      <x:c r="Q8" s="9"/>
+      <x:c r="K8" s="8" t="n">
+        <x:v>8405</x:v>
+      </x:c>
+      <x:c r="L8" s="8" t="n">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="n">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="N8" s="8" t="n">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="O8" s="8" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="P8" s="8" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="Q8" s="9" t="n">
+        <x:v>91233</x:v>
+      </x:c>
       <x:c r="R8" s="9"/>
       <x:c r="S8" s="9"/>
       <x:c r="T8" s="8"/>
       <x:c r="U8" s="8"/>
+      <x:c r="V8" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Google Ads</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W8" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X8" s="12" t="inlineStr">
+        <x:is>
+          <x:t>GOOGLE-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="9" ht="23" customHeight="1">
-      <x:c r="A9" s="7"/>
-      <x:c r="B9" s="6"/>
-      <x:c r="C9" s="6"/>
-      <x:c r="D9" s="6"/>
+      <x:c r="A9" s="7" t="n">
+        <x:v>46173</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Prospecting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Static image</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="6"/>
-      <x:c r="G9" s="9"/>
-      <x:c r="H9" s="9"/>
-      <x:c r="I9" s="8"/>
+      <x:c r="G9" s="9" t="n">
+        <x:v>3602</x:v>
+      </x:c>
+      <x:c r="H9" s="9" t="n">
+        <x:v>7743</x:v>
+      </x:c>
+      <x:c r="I9" s="8" t="n">
+        <x:v>216000</x:v>
+      </x:c>
       <x:c r="J9" s="8"/>
-      <x:c r="K9" s="8"/>
-      <x:c r="L9" s="8"/>
-      <x:c r="M9" s="8"/>
-      <x:c r="N9" s="8"/>
-      <x:c r="O9" s="8"/>
-      <x:c r="P9" s="8"/>
-      <x:c r="Q9" s="9"/>
+      <x:c r="K9" s="8" t="n">
+        <x:v>3895</x:v>
+      </x:c>
+      <x:c r="L9" s="8" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="M9" s="8" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N9" s="8" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="O9" s="8" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="P9" s="8" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="Q9" s="9" t="n">
+        <x:v>13938</x:v>
+      </x:c>
       <x:c r="R9" s="9"/>
       <x:c r="S9" s="9"/>
       <x:c r="T9" s="8"/>
       <x:c r="U9" s="8"/>
+      <x:c r="V9" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Meta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W9" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Facebook</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X9" s="12" t="inlineStr">
+        <x:is>
+          <x:t>META-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
-      <x:c r="A10" s="7"/>
-      <x:c r="B10" s="6"/>
-      <x:c r="C10" s="6"/>
-      <x:c r="D10" s="6"/>
+      <x:c r="A10" s="7" t="n">
+        <x:v>46173</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Prospecting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Short video</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E10" s="6"/>
       <x:c r="F10" s="6"/>
-      <x:c r="G10" s="9"/>
-      <x:c r="H10" s="9"/>
-      <x:c r="I10" s="8"/>
+      <x:c r="G10" s="9" t="n">
+        <x:v>3152</x:v>
+      </x:c>
+      <x:c r="H10" s="9" t="n">
+        <x:v>6775</x:v>
+      </x:c>
+      <x:c r="I10" s="8" t="n">
+        <x:v>189000</x:v>
+      </x:c>
       <x:c r="J10" s="8"/>
-      <x:c r="K10" s="8"/>
-      <x:c r="L10" s="8"/>
-      <x:c r="M10" s="8"/>
-      <x:c r="N10" s="8"/>
-      <x:c r="O10" s="8"/>
-      <x:c r="P10" s="8"/>
-      <x:c r="Q10" s="9"/>
+      <x:c r="K10" s="8" t="n">
+        <x:v>3408</x:v>
+      </x:c>
+      <x:c r="L10" s="8" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M10" s="8" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="N10" s="8" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O10" s="8" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P10" s="8" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Q10" s="9" t="n">
+        <x:v>12195</x:v>
+      </x:c>
       <x:c r="R10" s="9"/>
       <x:c r="S10" s="9"/>
       <x:c r="T10" s="8"/>
       <x:c r="U10" s="8"/>
+      <x:c r="V10" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Meta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W10" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Instagram</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X10" s="12" t="inlineStr">
+        <x:is>
+          <x:t>META-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
-      <x:c r="A11" s="7"/>
-      <x:c r="B11" s="6"/>
-      <x:c r="C11" s="6"/>
-      <x:c r="D11" s="6"/>
+      <x:c r="A11" s="7" t="n">
+        <x:v>46173</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Business leads</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Static image</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E11" s="6"/>
       <x:c r="F11" s="6"/>
-      <x:c r="G11" s="9"/>
-      <x:c r="H11" s="9"/>
-      <x:c r="I11" s="8"/>
+      <x:c r="G11" s="9" t="n">
+        <x:v>2251</x:v>
+      </x:c>
+      <x:c r="H11" s="9" t="n">
+        <x:v>4840</x:v>
+      </x:c>
+      <x:c r="I11" s="8" t="n">
+        <x:v>135000</x:v>
+      </x:c>
       <x:c r="J11" s="8"/>
-      <x:c r="K11" s="8"/>
-      <x:c r="L11" s="8"/>
-      <x:c r="M11" s="8"/>
-      <x:c r="N11" s="8"/>
-      <x:c r="O11" s="8"/>
-      <x:c r="P11" s="8"/>
-      <x:c r="Q11" s="9"/>
+      <x:c r="K11" s="8" t="n">
+        <x:v>2435</x:v>
+      </x:c>
+      <x:c r="L11" s="8" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="M11" s="8" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N11" s="8" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="O11" s="8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="P11" s="8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="Q11" s="9" t="n">
+        <x:v>8711</x:v>
+      </x:c>
       <x:c r="R11" s="9"/>
       <x:c r="S11" s="9"/>
       <x:c r="T11" s="8"/>
       <x:c r="U11" s="8"/>
+      <x:c r="V11" s="12" t="inlineStr">
+        <x:is>
+          <x:t>LinkedIn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W11" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Feed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X11" s="12" t="inlineStr">
+        <x:is>
+          <x:t>LI-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
-      <x:c r="A12" s="7"/>
-      <x:c r="B12" s="6"/>
-      <x:c r="C12" s="6"/>
+      <x:c r="A12" s="7" t="n">
+        <x:v>46173</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Email</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Lifecycle</x:t>
+        </x:is>
+      </x:c>
       <x:c r="D12" s="6"/>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="6"/>
-      <x:c r="G12" s="9"/>
-      <x:c r="H12" s="9"/>
-      <x:c r="I12" s="8"/>
+      <x:c r="G12" s="9" t="n">
+        <x:v>1759</x:v>
+      </x:c>
+      <x:c r="H12" s="9" t="n">
+        <x:v>22018</x:v>
+      </x:c>
+      <x:c r="I12" s="8" t="n">
+        <x:v>37000</x:v>
+      </x:c>
       <x:c r="J12" s="8"/>
-      <x:c r="K12" s="8"/>
-      <x:c r="L12" s="8"/>
-      <x:c r="M12" s="8"/>
-      <x:c r="N12" s="8"/>
-      <x:c r="O12" s="8"/>
-      <x:c r="P12" s="8"/>
-      <x:c r="Q12" s="9"/>
+      <x:c r="K12" s="8" t="n">
+        <x:v>5535</x:v>
+      </x:c>
+      <x:c r="L12" s="8" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="M12" s="8" t="n">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="N12" s="8" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="O12" s="8" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="P12" s="8" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="Q12" s="9" t="n">
+        <x:v>39632</x:v>
+      </x:c>
       <x:c r="R12" s="9"/>
       <x:c r="S12" s="9"/>
       <x:c r="T12" s="8"/>
       <x:c r="U12" s="8"/>
+      <x:c r="V12" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Email</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W12" s="12"/>
+      <x:c r="X12" s="12" t="inlineStr">
+        <x:is>
+          <x:t>EMAIL-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="13" ht="23" customHeight="1">
-      <x:c r="A13" s="7"/>
-      <x:c r="B13" s="6"/>
-      <x:c r="C13" s="6"/>
+      <x:c r="A13" s="7" t="n">
+        <x:v>46173</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Organic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Content</x:t>
+        </x:is>
+      </x:c>
       <x:c r="D13" s="6"/>
       <x:c r="E13" s="6"/>
       <x:c r="F13" s="6"/>
-      <x:c r="G13" s="9"/>
-      <x:c r="H13" s="9"/>
-      <x:c r="I13" s="8"/>
+      <x:c r="G13" s="9" t="n">
+        <x:v>931</x:v>
+      </x:c>
+      <x:c r="H13" s="9" t="n">
+        <x:v>10464</x:v>
+      </x:c>
+      <x:c r="I13" s="8" t="n">
+        <x:v>98000</x:v>
+      </x:c>
       <x:c r="J13" s="8"/>
-      <x:c r="K13" s="8"/>
-      <x:c r="L13" s="8"/>
-      <x:c r="M13" s="8"/>
-      <x:c r="N13" s="8"/>
-      <x:c r="O13" s="8"/>
-      <x:c r="P13" s="8"/>
-      <x:c r="Q13" s="9"/>
+      <x:c r="K13" s="8" t="n">
+        <x:v>4305</x:v>
+      </x:c>
+      <x:c r="L13" s="8" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="M13" s="8" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="N13" s="8" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O13" s="8" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P13" s="8" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q13" s="9" t="n">
+        <x:v>18835</x:v>
+      </x:c>
       <x:c r="R13" s="9"/>
       <x:c r="S13" s="9"/>
       <x:c r="T13" s="8"/>
       <x:c r="U13" s="8"/>
+      <x:c r="V13" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Organic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W13" s="12"/>
+      <x:c r="X13" s="12" t="inlineStr">
+        <x:is>
+          <x:t>ORGANIC-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="14" ht="23" customHeight="1">
-      <x:c r="A14" s="7"/>
-      <x:c r="B14" s="6"/>
-      <x:c r="C14" s="6"/>
-      <x:c r="D14" s="6"/>
+      <x:c r="A14" s="7" t="n">
+        <x:v>46203</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Brand &amp; non-brand</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Search text</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E14" s="6"/>
       <x:c r="F14" s="6"/>
-      <x:c r="G14" s="9"/>
-      <x:c r="H14" s="9"/>
-      <x:c r="I14" s="8"/>
+      <x:c r="G14" s="9" t="n">
+        <x:v>13375</x:v>
+      </x:c>
+      <x:c r="H14" s="9" t="n">
+        <x:v>54870</x:v>
+      </x:c>
+      <x:c r="I14" s="8" t="n">
+        <x:v>190000</x:v>
+      </x:c>
       <x:c r="J14" s="8"/>
-      <x:c r="K14" s="8"/>
-      <x:c r="L14" s="8"/>
-      <x:c r="M14" s="8"/>
-      <x:c r="N14" s="8"/>
-      <x:c r="O14" s="8"/>
-      <x:c r="P14" s="8"/>
-      <x:c r="Q14" s="9"/>
+      <x:c r="K14" s="8" t="n">
+        <x:v>8610</x:v>
+      </x:c>
+      <x:c r="L14" s="8" t="n">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="M14" s="8" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="N14" s="8" t="n">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="O14" s="8" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="P14" s="8" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="Q14" s="9" t="n">
+        <x:v>98766</x:v>
+      </x:c>
       <x:c r="R14" s="9"/>
       <x:c r="S14" s="9"/>
       <x:c r="T14" s="8"/>
       <x:c r="U14" s="8"/>
+      <x:c r="V14" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Google Ads</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W14" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X14" s="12" t="inlineStr">
+        <x:is>
+          <x:t>GOOGLE-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
-      <x:c r="A15" s="7"/>
-      <x:c r="B15" s="6"/>
-      <x:c r="C15" s="6"/>
-      <x:c r="D15" s="6"/>
+      <x:c r="A15" s="7" t="n">
+        <x:v>46203</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Prospecting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Static image</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E15" s="6"/>
       <x:c r="F15" s="6"/>
-      <x:c r="G15" s="9"/>
-      <x:c r="H15" s="9"/>
-      <x:c r="I15" s="8"/>
+      <x:c r="G15" s="9" t="n">
+        <x:v>3724</x:v>
+      </x:c>
+      <x:c r="H15" s="9" t="n">
+        <x:v>7703</x:v>
+      </x:c>
+      <x:c r="I15" s="8" t="n">
+        <x:v>216000</x:v>
+      </x:c>
       <x:c r="J15" s="8"/>
-      <x:c r="K15" s="8"/>
-      <x:c r="L15" s="8"/>
-      <x:c r="M15" s="8"/>
-      <x:c r="N15" s="8"/>
-      <x:c r="O15" s="8"/>
-      <x:c r="P15" s="8"/>
-      <x:c r="Q15" s="9"/>
+      <x:c r="K15" s="8" t="n">
+        <x:v>3990</x:v>
+      </x:c>
+      <x:c r="L15" s="8" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="M15" s="8" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N15" s="8" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="O15" s="8" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="P15" s="8" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="Q15" s="9" t="n">
+        <x:v>13866</x:v>
+      </x:c>
       <x:c r="R15" s="9"/>
       <x:c r="S15" s="9"/>
       <x:c r="T15" s="8"/>
       <x:c r="U15" s="8"/>
+      <x:c r="V15" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Meta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W15" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Facebook</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X15" s="12" t="inlineStr">
+        <x:is>
+          <x:t>META-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
-      <x:c r="A16" s="7"/>
-      <x:c r="B16" s="6"/>
-      <x:c r="C16" s="6"/>
-      <x:c r="D16" s="6"/>
+      <x:c r="A16" s="7" t="n">
+        <x:v>46203</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Prospecting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Short video</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E16" s="6"/>
       <x:c r="F16" s="6"/>
-      <x:c r="G16" s="9"/>
-      <x:c r="H16" s="9"/>
-      <x:c r="I16" s="8"/>
+      <x:c r="G16" s="9" t="n">
+        <x:v>3258</x:v>
+      </x:c>
+      <x:c r="H16" s="9" t="n">
+        <x:v>6740</x:v>
+      </x:c>
+      <x:c r="I16" s="8" t="n">
+        <x:v>189000</x:v>
+      </x:c>
       <x:c r="J16" s="8"/>
-      <x:c r="K16" s="8"/>
-      <x:c r="L16" s="8"/>
-      <x:c r="M16" s="8"/>
-      <x:c r="N16" s="8"/>
-      <x:c r="O16" s="8"/>
-      <x:c r="P16" s="8"/>
-      <x:c r="Q16" s="9"/>
+      <x:c r="K16" s="8" t="n">
+        <x:v>3491</x:v>
+      </x:c>
+      <x:c r="L16" s="8" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="M16" s="8" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N16" s="8" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O16" s="8" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P16" s="8" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q16" s="9" t="n">
+        <x:v>12132</x:v>
+      </x:c>
       <x:c r="R16" s="9"/>
       <x:c r="S16" s="9"/>
       <x:c r="T16" s="8"/>
       <x:c r="U16" s="8"/>
+      <x:c r="V16" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Meta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W16" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Instagram</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X16" s="12" t="inlineStr">
+        <x:is>
+          <x:t>META-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="17" ht="23" customHeight="1">
-      <x:c r="A17" s="7"/>
-      <x:c r="B17" s="6"/>
-      <x:c r="C17" s="6"/>
-      <x:c r="D17" s="6"/>
+      <x:c r="A17" s="7" t="n">
+        <x:v>46203</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Business leads</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Static image</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E17" s="6"/>
       <x:c r="F17" s="6"/>
-      <x:c r="G17" s="9"/>
-      <x:c r="H17" s="9"/>
-      <x:c r="I17" s="8"/>
+      <x:c r="G17" s="9" t="n">
+        <x:v>2327</x:v>
+      </x:c>
+      <x:c r="H17" s="9" t="n">
+        <x:v>4815</x:v>
+      </x:c>
+      <x:c r="I17" s="8" t="n">
+        <x:v>135000</x:v>
+      </x:c>
       <x:c r="J17" s="8"/>
-      <x:c r="K17" s="8"/>
-      <x:c r="L17" s="8"/>
-      <x:c r="M17" s="8"/>
-      <x:c r="N17" s="8"/>
-      <x:c r="O17" s="8"/>
-      <x:c r="P17" s="8"/>
-      <x:c r="Q17" s="9"/>
+      <x:c r="K17" s="8" t="n">
+        <x:v>2494</x:v>
+      </x:c>
+      <x:c r="L17" s="8" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="M17" s="8" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N17" s="8" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="O17" s="8" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P17" s="8" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q17" s="9" t="n">
+        <x:v>8666</x:v>
+      </x:c>
       <x:c r="R17" s="9"/>
       <x:c r="S17" s="9"/>
       <x:c r="T17" s="8"/>
       <x:c r="U17" s="8"/>
+      <x:c r="V17" s="12" t="inlineStr">
+        <x:is>
+          <x:t>LinkedIn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W17" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Feed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X17" s="12" t="inlineStr">
+        <x:is>
+          <x:t>LI-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="18" ht="23" customHeight="1">
-      <x:c r="A18" s="7"/>
-      <x:c r="B18" s="6"/>
-      <x:c r="C18" s="6"/>
+      <x:c r="A18" s="7" t="n">
+        <x:v>46203</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Email</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Lifecycle</x:t>
+        </x:is>
+      </x:c>
       <x:c r="D18" s="6"/>
       <x:c r="E18" s="6"/>
       <x:c r="F18" s="6"/>
-      <x:c r="G18" s="9"/>
-      <x:c r="H18" s="9"/>
-      <x:c r="I18" s="8"/>
+      <x:c r="G18" s="9" t="n">
+        <x:v>1819</x:v>
+      </x:c>
+      <x:c r="H18" s="9" t="n">
+        <x:v>23836</x:v>
+      </x:c>
+      <x:c r="I18" s="8" t="n">
+        <x:v>37000</x:v>
+      </x:c>
       <x:c r="J18" s="8"/>
-      <x:c r="K18" s="8"/>
-      <x:c r="L18" s="8"/>
-      <x:c r="M18" s="8"/>
-      <x:c r="N18" s="8"/>
-      <x:c r="O18" s="8"/>
-      <x:c r="P18" s="8"/>
-      <x:c r="Q18" s="9"/>
+      <x:c r="K18" s="8" t="n">
+        <x:v>5670</x:v>
+      </x:c>
+      <x:c r="L18" s="8" t="n">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="M18" s="8" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="N18" s="8" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="O18" s="8" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="P18" s="8" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="Q18" s="9" t="n">
+        <x:v>42905</x:v>
+      </x:c>
       <x:c r="R18" s="9"/>
       <x:c r="S18" s="9"/>
       <x:c r="T18" s="8"/>
       <x:c r="U18" s="8"/>
+      <x:c r="V18" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Email</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W18" s="12"/>
+      <x:c r="X18" s="12" t="inlineStr">
+        <x:is>
+          <x:t>EMAIL-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
-      <x:c r="A19" s="7"/>
-      <x:c r="B19" s="6"/>
-      <x:c r="C19" s="6"/>
+      <x:c r="A19" s="7" t="n">
+        <x:v>46203</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Organic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Content</x:t>
+        </x:is>
+      </x:c>
       <x:c r="D19" s="6"/>
       <x:c r="E19" s="6"/>
       <x:c r="F19" s="6"/>
-      <x:c r="G19" s="9"/>
-      <x:c r="H19" s="9"/>
-      <x:c r="I19" s="8"/>
+      <x:c r="G19" s="9" t="n">
+        <x:v>963</x:v>
+      </x:c>
+      <x:c r="H19" s="9" t="n">
+        <x:v>11328</x:v>
+      </x:c>
+      <x:c r="I19" s="8" t="n">
+        <x:v>98000</x:v>
+      </x:c>
       <x:c r="J19" s="8"/>
-      <x:c r="K19" s="8"/>
-      <x:c r="L19" s="8"/>
-      <x:c r="M19" s="8"/>
-      <x:c r="N19" s="8"/>
-      <x:c r="O19" s="8"/>
-      <x:c r="P19" s="8"/>
-      <x:c r="Q19" s="9"/>
+      <x:c r="K19" s="8" t="n">
+        <x:v>4410</x:v>
+      </x:c>
+      <x:c r="L19" s="8" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="M19" s="8" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="N19" s="8" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="O19" s="8" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="P19" s="8" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="Q19" s="9" t="n">
+        <x:v>20390</x:v>
+      </x:c>
       <x:c r="R19" s="9"/>
       <x:c r="S19" s="9"/>
       <x:c r="T19" s="8"/>
       <x:c r="U19" s="8"/>
+      <x:c r="V19" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Organic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W19" s="12"/>
+      <x:c r="X19" s="12" t="inlineStr">
+        <x:is>
+          <x:t>ORGANIC-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="20" ht="23" customHeight="1">
-      <x:c r="A20" s="7"/>
-      <x:c r="B20" s="6"/>
-      <x:c r="C20" s="6"/>
-      <x:c r="D20" s="6"/>
+      <x:c r="A20" s="7" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C20" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Brand &amp; non-brand</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D20" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Search text</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E20" s="6"/>
       <x:c r="F20" s="6"/>
-      <x:c r="G20" s="9"/>
-      <x:c r="H20" s="9"/>
-      <x:c r="I20" s="8"/>
+      <x:c r="G20" s="9" t="n">
+        <x:v>13813</x:v>
+      </x:c>
+      <x:c r="H20" s="9" t="n">
+        <x:v>59055</x:v>
+      </x:c>
+      <x:c r="I20" s="8" t="n">
+        <x:v>190000</x:v>
+      </x:c>
       <x:c r="J20" s="8"/>
-      <x:c r="K20" s="8"/>
-      <x:c r="L20" s="8"/>
-      <x:c r="M20" s="8"/>
-      <x:c r="N20" s="8"/>
-      <x:c r="O20" s="8"/>
-      <x:c r="P20" s="8"/>
-      <x:c r="Q20" s="9"/>
+      <x:c r="K20" s="8" t="n">
+        <x:v>8815</x:v>
+      </x:c>
+      <x:c r="L20" s="8" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="M20" s="8" t="n">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="N20" s="8" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="O20" s="8" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="P20" s="8" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="Q20" s="9" t="n">
+        <x:v>106299</x:v>
+      </x:c>
       <x:c r="R20" s="9"/>
       <x:c r="S20" s="9"/>
       <x:c r="T20" s="8"/>
       <x:c r="U20" s="8"/>
+      <x:c r="V20" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Google Ads</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W20" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X20" s="12" t="inlineStr">
+        <x:is>
+          <x:t>GOOGLE-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="21" ht="23" customHeight="1">
-      <x:c r="A21" s="7"/>
-      <x:c r="B21" s="6"/>
-      <x:c r="C21" s="6"/>
-      <x:c r="D21" s="6"/>
+      <x:c r="A21" s="7" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C21" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Prospecting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Static image</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E21" s="6"/>
       <x:c r="F21" s="6"/>
-      <x:c r="G21" s="9"/>
-      <x:c r="H21" s="9"/>
-      <x:c r="I21" s="8"/>
+      <x:c r="G21" s="9" t="n">
+        <x:v>3846</x:v>
+      </x:c>
+      <x:c r="H21" s="9" t="n">
+        <x:v>7559</x:v>
+      </x:c>
+      <x:c r="I21" s="8" t="n">
+        <x:v>216000</x:v>
+      </x:c>
       <x:c r="J21" s="8"/>
-      <x:c r="K21" s="8"/>
-      <x:c r="L21" s="8"/>
-      <x:c r="M21" s="8"/>
-      <x:c r="N21" s="8"/>
-      <x:c r="O21" s="8"/>
-      <x:c r="P21" s="8"/>
-      <x:c r="Q21" s="9"/>
+      <x:c r="K21" s="8" t="n">
+        <x:v>4085</x:v>
+      </x:c>
+      <x:c r="L21" s="8" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="M21" s="8" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N21" s="8" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="O21" s="8" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="P21" s="8" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q21" s="9" t="n">
+        <x:v>13606</x:v>
+      </x:c>
       <x:c r="R21" s="9"/>
       <x:c r="S21" s="9"/>
       <x:c r="T21" s="8"/>
       <x:c r="U21" s="8"/>
+      <x:c r="V21" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Meta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W21" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Facebook</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X21" s="12" t="inlineStr">
+        <x:is>
+          <x:t>META-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
-      <x:c r="A22" s="7"/>
-      <x:c r="B22" s="6"/>
-      <x:c r="C22" s="6"/>
-      <x:c r="D22" s="6"/>
+      <x:c r="A22" s="7" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C22" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Prospecting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Short video</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E22" s="6"/>
       <x:c r="F22" s="6"/>
-      <x:c r="G22" s="9"/>
-      <x:c r="H22" s="9"/>
-      <x:c r="I22" s="8"/>
+      <x:c r="G22" s="9" t="n">
+        <x:v>3365</x:v>
+      </x:c>
+      <x:c r="H22" s="9" t="n">
+        <x:v>6614</x:v>
+      </x:c>
+      <x:c r="I22" s="8" t="n">
+        <x:v>189000</x:v>
+      </x:c>
       <x:c r="J22" s="8"/>
-      <x:c r="K22" s="8"/>
-      <x:c r="L22" s="8"/>
-      <x:c r="M22" s="8"/>
-      <x:c r="N22" s="8"/>
-      <x:c r="O22" s="8"/>
-      <x:c r="P22" s="8"/>
-      <x:c r="Q22" s="9"/>
+      <x:c r="K22" s="8" t="n">
+        <x:v>3575</x:v>
+      </x:c>
+      <x:c r="L22" s="8" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="M22" s="8" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="N22" s="8" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="O22" s="8" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="P22" s="8" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="Q22" s="9" t="n">
+        <x:v>11906</x:v>
+      </x:c>
       <x:c r="R22" s="9"/>
       <x:c r="S22" s="9"/>
       <x:c r="T22" s="8"/>
       <x:c r="U22" s="8"/>
+      <x:c r="V22" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Meta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W22" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Instagram</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X22" s="12" t="inlineStr">
+        <x:is>
+          <x:t>META-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
-      <x:c r="A23" s="7"/>
-      <x:c r="B23" s="6"/>
-      <x:c r="C23" s="6"/>
-      <x:c r="D23" s="6"/>
+      <x:c r="A23" s="7" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C23" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Business leads</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Static image</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E23" s="6"/>
       <x:c r="F23" s="6"/>
-      <x:c r="G23" s="9"/>
-      <x:c r="H23" s="9"/>
-      <x:c r="I23" s="8"/>
+      <x:c r="G23" s="9" t="n">
+        <x:v>2404</x:v>
+      </x:c>
+      <x:c r="H23" s="9" t="n">
+        <x:v>4725</x:v>
+      </x:c>
+      <x:c r="I23" s="8" t="n">
+        <x:v>135000</x:v>
+      </x:c>
       <x:c r="J23" s="8"/>
-      <x:c r="K23" s="8"/>
-      <x:c r="L23" s="8"/>
-      <x:c r="M23" s="8"/>
-      <x:c r="N23" s="8"/>
-      <x:c r="O23" s="8"/>
-      <x:c r="P23" s="8"/>
-      <x:c r="Q23" s="9"/>
+      <x:c r="K23" s="8" t="n">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="L23" s="8" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="M23" s="8" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="N23" s="8" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="O23" s="8" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="P23" s="8" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="Q23" s="9" t="n">
+        <x:v>8504</x:v>
+      </x:c>
       <x:c r="R23" s="9"/>
       <x:c r="S23" s="9"/>
       <x:c r="T23" s="8"/>
       <x:c r="U23" s="8"/>
+      <x:c r="V23" s="12" t="inlineStr">
+        <x:is>
+          <x:t>LinkedIn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W23" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Feed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X23" s="12" t="inlineStr">
+        <x:is>
+          <x:t>LI-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
-      <x:c r="A24" s="7"/>
-      <x:c r="B24" s="6"/>
-      <x:c r="C24" s="6"/>
+      <x:c r="A24" s="7" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Email</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C24" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Lifecycle</x:t>
+        </x:is>
+      </x:c>
       <x:c r="D24" s="6"/>
       <x:c r="E24" s="6"/>
       <x:c r="F24" s="6"/>
-      <x:c r="G24" s="9"/>
-      <x:c r="H24" s="9"/>
-      <x:c r="I24" s="8"/>
+      <x:c r="G24" s="9" t="n">
+        <x:v>1879</x:v>
+      </x:c>
+      <x:c r="H24" s="9" t="n">
+        <x:v>25654</x:v>
+      </x:c>
+      <x:c r="I24" s="8" t="n">
+        <x:v>37000</x:v>
+      </x:c>
       <x:c r="J24" s="8"/>
-      <x:c r="K24" s="8"/>
-      <x:c r="L24" s="8"/>
-      <x:c r="M24" s="8"/>
-      <x:c r="N24" s="8"/>
-      <x:c r="O24" s="8"/>
-      <x:c r="P24" s="8"/>
-      <x:c r="Q24" s="9"/>
+      <x:c r="K24" s="8" t="n">
+        <x:v>5805</x:v>
+      </x:c>
+      <x:c r="L24" s="8" t="n">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="M24" s="8" t="n">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="N24" s="8" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="O24" s="8" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="P24" s="8" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="Q24" s="9" t="n">
+        <x:v>46177</x:v>
+      </x:c>
       <x:c r="R24" s="9"/>
       <x:c r="S24" s="9"/>
       <x:c r="T24" s="8"/>
       <x:c r="U24" s="8"/>
+      <x:c r="V24" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Email</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W24" s="12"/>
+      <x:c r="X24" s="12" t="inlineStr">
+        <x:is>
+          <x:t>EMAIL-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
-      <x:c r="A25" s="7"/>
-      <x:c r="B25" s="6"/>
-      <x:c r="C25" s="6"/>
+      <x:c r="A25" s="7" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Organic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C25" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Content</x:t>
+        </x:is>
+      </x:c>
       <x:c r="D25" s="6"/>
       <x:c r="E25" s="6"/>
       <x:c r="F25" s="6"/>
-      <x:c r="G25" s="9"/>
-      <x:c r="H25" s="9"/>
-      <x:c r="I25" s="8"/>
+      <x:c r="G25" s="9" t="n">
+        <x:v>995</x:v>
+      </x:c>
+      <x:c r="H25" s="9" t="n">
+        <x:v>12192</x:v>
+      </x:c>
+      <x:c r="I25" s="8" t="n">
+        <x:v>98000</x:v>
+      </x:c>
       <x:c r="J25" s="8"/>
-      <x:c r="K25" s="8"/>
-      <x:c r="L25" s="8"/>
-      <x:c r="M25" s="8"/>
-      <x:c r="N25" s="8"/>
-      <x:c r="O25" s="8"/>
-      <x:c r="P25" s="8"/>
-      <x:c r="Q25" s="9"/>
+      <x:c r="K25" s="8" t="n">
+        <x:v>4515</x:v>
+      </x:c>
+      <x:c r="L25" s="8" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="M25" s="8" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="N25" s="8" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O25" s="8" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="P25" s="8" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="Q25" s="9" t="n">
+        <x:v>21946</x:v>
+      </x:c>
       <x:c r="R25" s="9"/>
       <x:c r="S25" s="9"/>
       <x:c r="T25" s="8"/>
       <x:c r="U25" s="8"/>
+      <x:c r="V25" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Organic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W25" s="12"/>
+      <x:c r="X25" s="12" t="inlineStr">
+        <x:is>
+          <x:t>ORGANIC-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
-      <x:c r="A26" s="7"/>
-      <x:c r="B26" s="6"/>
-      <x:c r="C26" s="6"/>
-      <x:c r="D26" s="6"/>
+      <x:c r="A26" s="7" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C26" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Brand &amp; non-brand</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D26" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Search text</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E26" s="6"/>
       <x:c r="F26" s="6"/>
-      <x:c r="G26" s="9"/>
-      <x:c r="H26" s="9"/>
-      <x:c r="I26" s="8"/>
+      <x:c r="G26" s="9" t="n">
+        <x:v>14250</x:v>
+      </x:c>
+      <x:c r="H26" s="9" t="n">
+        <x:v>63240</x:v>
+      </x:c>
+      <x:c r="I26" s="8" t="n">
+        <x:v>190000</x:v>
+      </x:c>
       <x:c r="J26" s="8"/>
-      <x:c r="K26" s="8"/>
-      <x:c r="L26" s="8"/>
-      <x:c r="M26" s="8"/>
-      <x:c r="N26" s="8"/>
-      <x:c r="O26" s="8"/>
-      <x:c r="P26" s="8"/>
-      <x:c r="Q26" s="9"/>
+      <x:c r="K26" s="8" t="n">
+        <x:v>9020</x:v>
+      </x:c>
+      <x:c r="L26" s="8" t="n">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="M26" s="8" t="n">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="N26" s="8" t="n">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="O26" s="8" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="P26" s="8" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="Q26" s="9" t="n">
+        <x:v>113832</x:v>
+      </x:c>
       <x:c r="R26" s="9"/>
       <x:c r="S26" s="9"/>
       <x:c r="T26" s="8"/>
       <x:c r="U26" s="8"/>
+      <x:c r="V26" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Google Ads</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W26" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X26" s="12" t="inlineStr">
+        <x:is>
+          <x:t>GOOGLE-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
-      <x:c r="A27" s="7"/>
-      <x:c r="B27" s="6"/>
-      <x:c r="C27" s="6"/>
-      <x:c r="D27" s="6"/>
+      <x:c r="A27" s="7" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C27" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Prospecting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D27" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Static image</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E27" s="6"/>
       <x:c r="F27" s="6"/>
-      <x:c r="G27" s="9"/>
-      <x:c r="H27" s="9"/>
-      <x:c r="I27" s="8"/>
+      <x:c r="G27" s="9" t="n">
+        <x:v>3967</x:v>
+      </x:c>
+      <x:c r="H27" s="9" t="n">
+        <x:v>7311</x:v>
+      </x:c>
+      <x:c r="I27" s="8" t="n">
+        <x:v>216000</x:v>
+      </x:c>
       <x:c r="J27" s="8"/>
-      <x:c r="K27" s="8"/>
-      <x:c r="L27" s="8"/>
-      <x:c r="M27" s="8"/>
-      <x:c r="N27" s="8"/>
-      <x:c r="O27" s="8"/>
-      <x:c r="P27" s="8"/>
-      <x:c r="Q27" s="9"/>
+      <x:c r="K27" s="8" t="n">
+        <x:v>4180</x:v>
+      </x:c>
+      <x:c r="L27" s="8" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="M27" s="8" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N27" s="8" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O27" s="8" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="P27" s="8" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q27" s="9" t="n">
+        <x:v>13160</x:v>
+      </x:c>
       <x:c r="R27" s="9"/>
       <x:c r="S27" s="9"/>
       <x:c r="T27" s="8"/>
       <x:c r="U27" s="8"/>
+      <x:c r="V27" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Meta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W27" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Facebook</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X27" s="12" t="inlineStr">
+        <x:is>
+          <x:t>META-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="28" ht="23" customHeight="1">
-      <x:c r="A28" s="7"/>
-      <x:c r="B28" s="6"/>
-      <x:c r="C28" s="6"/>
-      <x:c r="D28" s="6"/>
+      <x:c r="A28" s="7" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C28" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Prospecting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D28" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Short video</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E28" s="6"/>
       <x:c r="F28" s="6"/>
-      <x:c r="G28" s="9"/>
-      <x:c r="H28" s="9"/>
-      <x:c r="I28" s="8"/>
+      <x:c r="G28" s="9" t="n">
+        <x:v>3471</x:v>
+      </x:c>
+      <x:c r="H28" s="9" t="n">
+        <x:v>6397</x:v>
+      </x:c>
+      <x:c r="I28" s="8" t="n">
+        <x:v>189000</x:v>
+      </x:c>
       <x:c r="J28" s="8"/>
-      <x:c r="K28" s="8"/>
-      <x:c r="L28" s="8"/>
-      <x:c r="M28" s="8"/>
-      <x:c r="N28" s="8"/>
-      <x:c r="O28" s="8"/>
-      <x:c r="P28" s="8"/>
-      <x:c r="Q28" s="9"/>
+      <x:c r="K28" s="8" t="n">
+        <x:v>3657</x:v>
+      </x:c>
+      <x:c r="L28" s="8" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="M28" s="8" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="N28" s="8" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="O28" s="8" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="P28" s="8" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="Q28" s="9" t="n">
+        <x:v>11515</x:v>
+      </x:c>
       <x:c r="R28" s="9"/>
       <x:c r="S28" s="9"/>
       <x:c r="T28" s="8"/>
       <x:c r="U28" s="8"/>
+      <x:c r="V28" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Meta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W28" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Instagram</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X28" s="12" t="inlineStr">
+        <x:is>
+          <x:t>META-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="29" ht="23" customHeight="1">
-      <x:c r="A29" s="7"/>
-      <x:c r="B29" s="6"/>
-      <x:c r="C29" s="6"/>
-      <x:c r="D29" s="6"/>
+      <x:c r="A29" s="7" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C29" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Business leads</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Static image</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E29" s="6"/>
       <x:c r="F29" s="6"/>
-      <x:c r="G29" s="9"/>
-      <x:c r="H29" s="9"/>
-      <x:c r="I29" s="8"/>
+      <x:c r="G29" s="9" t="n">
+        <x:v>2480</x:v>
+      </x:c>
+      <x:c r="H29" s="9" t="n">
+        <x:v>4570</x:v>
+      </x:c>
+      <x:c r="I29" s="8" t="n">
+        <x:v>135000</x:v>
+      </x:c>
       <x:c r="J29" s="8"/>
-      <x:c r="K29" s="8"/>
-      <x:c r="L29" s="8"/>
-      <x:c r="M29" s="8"/>
-      <x:c r="N29" s="8"/>
-      <x:c r="O29" s="8"/>
-      <x:c r="P29" s="8"/>
-      <x:c r="Q29" s="9"/>
+      <x:c r="K29" s="8" t="n">
+        <x:v>2613</x:v>
+      </x:c>
+      <x:c r="L29" s="8" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M29" s="8" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="N29" s="8" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="O29" s="8" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P29" s="8" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q29" s="9" t="n">
+        <x:v>8225</x:v>
+      </x:c>
       <x:c r="R29" s="9"/>
       <x:c r="S29" s="9"/>
       <x:c r="T29" s="8"/>
       <x:c r="U29" s="8"/>
+      <x:c r="V29" s="12" t="inlineStr">
+        <x:is>
+          <x:t>LinkedIn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W29" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Feed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X29" s="12" t="inlineStr">
+        <x:is>
+          <x:t>LI-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="30" ht="23" customHeight="1">
-      <x:c r="A30" s="7"/>
-      <x:c r="B30" s="6"/>
-      <x:c r="C30" s="6"/>
+      <x:c r="A30" s="7" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Email</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C30" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Lifecycle</x:t>
+        </x:is>
+      </x:c>
       <x:c r="D30" s="6"/>
       <x:c r="E30" s="6"/>
       <x:c r="F30" s="6"/>
-      <x:c r="G30" s="9"/>
-      <x:c r="H30" s="9"/>
-      <x:c r="I30" s="8"/>
+      <x:c r="G30" s="9" t="n">
+        <x:v>1938</x:v>
+      </x:c>
+      <x:c r="H30" s="9" t="n">
+        <x:v>27472</x:v>
+      </x:c>
+      <x:c r="I30" s="8" t="n">
+        <x:v>37000</x:v>
+      </x:c>
       <x:c r="J30" s="8"/>
-      <x:c r="K30" s="8"/>
-      <x:c r="L30" s="8"/>
-      <x:c r="M30" s="8"/>
-      <x:c r="N30" s="8"/>
-      <x:c r="O30" s="8"/>
-      <x:c r="P30" s="8"/>
-      <x:c r="Q30" s="9"/>
+      <x:c r="K30" s="8" t="n">
+        <x:v>5940</x:v>
+      </x:c>
+      <x:c r="L30" s="8" t="n">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="M30" s="8" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="N30" s="8" t="n">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="O30" s="8" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="P30" s="8" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="Q30" s="9" t="n">
+        <x:v>49450</x:v>
+      </x:c>
       <x:c r="R30" s="9"/>
       <x:c r="S30" s="9"/>
       <x:c r="T30" s="8"/>
       <x:c r="U30" s="8"/>
+      <x:c r="V30" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Email</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W30" s="12"/>
+      <x:c r="X30" s="12" t="inlineStr">
+        <x:is>
+          <x:t>EMAIL-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="31" ht="23" customHeight="1">
-      <x:c r="A31" s="7"/>
-      <x:c r="B31" s="6"/>
-      <x:c r="C31" s="6"/>
+      <x:c r="A31" s="7" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Organic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C31" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Content</x:t>
+        </x:is>
+      </x:c>
       <x:c r="D31" s="6"/>
       <x:c r="E31" s="6"/>
       <x:c r="F31" s="6"/>
-      <x:c r="G31" s="9"/>
-      <x:c r="H31" s="9"/>
-      <x:c r="I31" s="8"/>
+      <x:c r="G31" s="9" t="n">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c r="H31" s="9" t="n">
+        <x:v>13056</x:v>
+      </x:c>
+      <x:c r="I31" s="8" t="n">
+        <x:v>98000</x:v>
+      </x:c>
       <x:c r="J31" s="8"/>
-      <x:c r="K31" s="8"/>
-      <x:c r="L31" s="8"/>
-      <x:c r="M31" s="8"/>
-      <x:c r="N31" s="8"/>
-      <x:c r="O31" s="8"/>
-      <x:c r="P31" s="8"/>
-      <x:c r="Q31" s="9"/>
+      <x:c r="K31" s="8" t="n">
+        <x:v>4620</x:v>
+      </x:c>
+      <x:c r="L31" s="8" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="M31" s="8" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N31" s="8" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="O31" s="8" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P31" s="8" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q31" s="9" t="n">
+        <x:v>23501</x:v>
+      </x:c>
       <x:c r="R31" s="9"/>
       <x:c r="S31" s="9"/>
       <x:c r="T31" s="8"/>
       <x:c r="U31" s="8"/>
+      <x:c r="V31" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Organic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W31" s="12"/>
+      <x:c r="X31" s="12" t="inlineStr">
+        <x:is>
+          <x:t>ORGANIC-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="32" ht="23" customHeight="1">
-      <x:c r="A32" s="7"/>
-      <x:c r="B32" s="6"/>
-      <x:c r="C32" s="6"/>
-      <x:c r="D32" s="6"/>
+      <x:c r="A32" s="7" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="B32" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C32" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Brand &amp; non-brand</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Search text</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E32" s="6"/>
       <x:c r="F32" s="6"/>
-      <x:c r="G32" s="9"/>
-      <x:c r="H32" s="9"/>
-      <x:c r="I32" s="8"/>
+      <x:c r="G32" s="9" t="n">
+        <x:v>14688</x:v>
+      </x:c>
+      <x:c r="H32" s="9" t="n">
+        <x:v>67425</x:v>
+      </x:c>
+      <x:c r="I32" s="8" t="n">
+        <x:v>190000</x:v>
+      </x:c>
       <x:c r="J32" s="8"/>
-      <x:c r="K32" s="8"/>
-      <x:c r="L32" s="8"/>
-      <x:c r="M32" s="8"/>
-      <x:c r="N32" s="8"/>
-      <x:c r="O32" s="8"/>
-      <x:c r="P32" s="8"/>
-      <x:c r="Q32" s="9"/>
+      <x:c r="K32" s="8" t="n">
+        <x:v>9225</x:v>
+      </x:c>
+      <x:c r="L32" s="8" t="n">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="M32" s="8" t="n">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="N32" s="8" t="n">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="O32" s="8" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="P32" s="8" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="Q32" s="9" t="n">
+        <x:v>121365</x:v>
+      </x:c>
       <x:c r="R32" s="9"/>
       <x:c r="S32" s="9"/>
       <x:c r="T32" s="8"/>
       <x:c r="U32" s="8"/>
+      <x:c r="V32" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Google Ads</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W32" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X32" s="12" t="inlineStr">
+        <x:is>
+          <x:t>GOOGLE-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="33" ht="23" customHeight="1">
-      <x:c r="A33" s="7"/>
-      <x:c r="B33" s="6"/>
-      <x:c r="C33" s="6"/>
-      <x:c r="D33" s="6"/>
+      <x:c r="A33" s="7" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C33" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Prospecting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D33" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Static image</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E33" s="6"/>
       <x:c r="F33" s="6"/>
-      <x:c r="G33" s="9"/>
-      <x:c r="H33" s="9"/>
-      <x:c r="I33" s="8"/>
+      <x:c r="G33" s="9" t="n">
+        <x:v>4089</x:v>
+      </x:c>
+      <x:c r="H33" s="9" t="n">
+        <x:v>6960</x:v>
+      </x:c>
+      <x:c r="I33" s="8" t="n">
+        <x:v>216000</x:v>
+      </x:c>
       <x:c r="J33" s="8"/>
-      <x:c r="K33" s="8"/>
-      <x:c r="L33" s="8"/>
-      <x:c r="M33" s="8"/>
-      <x:c r="N33" s="8"/>
-      <x:c r="O33" s="8"/>
-      <x:c r="P33" s="8"/>
-      <x:c r="Q33" s="9"/>
+      <x:c r="K33" s="8" t="n">
+        <x:v>4275</x:v>
+      </x:c>
+      <x:c r="L33" s="8" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="M33" s="8" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="N33" s="8" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O33" s="8" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P33" s="8" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q33" s="9" t="n">
+        <x:v>12528</x:v>
+      </x:c>
       <x:c r="R33" s="9"/>
       <x:c r="S33" s="9"/>
       <x:c r="T33" s="8"/>
       <x:c r="U33" s="8"/>
+      <x:c r="V33" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Meta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W33" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Facebook</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X33" s="12" t="inlineStr">
+        <x:is>
+          <x:t>META-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="34" ht="23" customHeight="1">
-      <x:c r="A34" s="7"/>
-      <x:c r="B34" s="6"/>
-      <x:c r="C34" s="6"/>
-      <x:c r="D34" s="6"/>
+      <x:c r="A34" s="7" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="B34" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C34" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Prospecting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D34" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Short video</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E34" s="6"/>
       <x:c r="F34" s="6"/>
-      <x:c r="G34" s="9"/>
-      <x:c r="H34" s="9"/>
-      <x:c r="I34" s="8"/>
+      <x:c r="G34" s="9" t="n">
+        <x:v>3578</x:v>
+      </x:c>
+      <x:c r="H34" s="9" t="n">
+        <x:v>6090</x:v>
+      </x:c>
+      <x:c r="I34" s="8" t="n">
+        <x:v>189000</x:v>
+      </x:c>
       <x:c r="J34" s="8"/>
-      <x:c r="K34" s="8"/>
-      <x:c r="L34" s="8"/>
-      <x:c r="M34" s="8"/>
-      <x:c r="N34" s="8"/>
-      <x:c r="O34" s="8"/>
-      <x:c r="P34" s="8"/>
-      <x:c r="Q34" s="9"/>
+      <x:c r="K34" s="8" t="n">
+        <x:v>3741</x:v>
+      </x:c>
+      <x:c r="L34" s="8" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="M34" s="8" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N34" s="8" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O34" s="8" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="P34" s="8" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q34" s="9" t="n">
+        <x:v>10962</x:v>
+      </x:c>
       <x:c r="R34" s="9"/>
       <x:c r="S34" s="9"/>
       <x:c r="T34" s="8"/>
       <x:c r="U34" s="8"/>
+      <x:c r="V34" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Meta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W34" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Instagram</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X34" s="12" t="inlineStr">
+        <x:is>
+          <x:t>META-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="35" ht="23" customHeight="1">
-      <x:c r="A35" s="7"/>
-      <x:c r="B35" s="6"/>
-      <x:c r="C35" s="6"/>
-      <x:c r="D35" s="6"/>
+      <x:c r="A35" s="7" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="B35" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Paid social</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C35" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Business leads</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D35" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Static image</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E35" s="6"/>
       <x:c r="F35" s="6"/>
-      <x:c r="G35" s="9"/>
-      <x:c r="H35" s="9"/>
-      <x:c r="I35" s="8"/>
+      <x:c r="G35" s="9" t="n">
+        <x:v>2556</x:v>
+      </x:c>
+      <x:c r="H35" s="9" t="n">
+        <x:v>4350</x:v>
+      </x:c>
+      <x:c r="I35" s="8" t="n">
+        <x:v>135000</x:v>
+      </x:c>
       <x:c r="J35" s="8"/>
-      <x:c r="K35" s="8"/>
-      <x:c r="L35" s="8"/>
-      <x:c r="M35" s="8"/>
-      <x:c r="N35" s="8"/>
-      <x:c r="O35" s="8"/>
-      <x:c r="P35" s="8"/>
-      <x:c r="Q35" s="9"/>
+      <x:c r="K35" s="8" t="n">
+        <x:v>2672</x:v>
+      </x:c>
+      <x:c r="L35" s="8" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M35" s="8" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="N35" s="8" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="O35" s="8" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="P35" s="8" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="Q35" s="9" t="n">
+        <x:v>7830</x:v>
+      </x:c>
       <x:c r="R35" s="9"/>
       <x:c r="S35" s="9"/>
       <x:c r="T35" s="8"/>
       <x:c r="U35" s="8"/>
+      <x:c r="V35" s="12" t="inlineStr">
+        <x:is>
+          <x:t>LinkedIn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W35" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Feed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X35" s="12" t="inlineStr">
+        <x:is>
+          <x:t>LI-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="36" ht="23" customHeight="1">
-      <x:c r="A36" s="7"/>
-      <x:c r="B36" s="6"/>
-      <x:c r="C36" s="6"/>
+      <x:c r="A36" s="7" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="B36" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Email</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C36" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Lifecycle</x:t>
+        </x:is>
+      </x:c>
       <x:c r="D36" s="6"/>
       <x:c r="E36" s="6"/>
       <x:c r="F36" s="6"/>
-      <x:c r="G36" s="9"/>
-      <x:c r="H36" s="9"/>
-      <x:c r="I36" s="8"/>
+      <x:c r="G36" s="9" t="n">
+        <x:v>1998</x:v>
+      </x:c>
+      <x:c r="H36" s="9" t="n">
+        <x:v>29290</x:v>
+      </x:c>
+      <x:c r="I36" s="8" t="n">
+        <x:v>37000</x:v>
+      </x:c>
       <x:c r="J36" s="8"/>
-      <x:c r="K36" s="8"/>
-      <x:c r="L36" s="8"/>
-      <x:c r="M36" s="8"/>
-      <x:c r="N36" s="8"/>
-      <x:c r="O36" s="8"/>
-      <x:c r="P36" s="8"/>
-      <x:c r="Q36" s="9"/>
+      <x:c r="K36" s="8" t="n">
+        <x:v>6075</x:v>
+      </x:c>
+      <x:c r="L36" s="8" t="n">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="M36" s="8" t="n">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="N36" s="8" t="n">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="O36" s="8" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="P36" s="8" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="Q36" s="9" t="n">
+        <x:v>52722</x:v>
+      </x:c>
       <x:c r="R36" s="9"/>
       <x:c r="S36" s="9"/>
       <x:c r="T36" s="8"/>
       <x:c r="U36" s="8"/>
+      <x:c r="V36" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Email</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W36" s="12"/>
+      <x:c r="X36" s="12" t="inlineStr">
+        <x:is>
+          <x:t>EMAIL-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="37" ht="23" customHeight="1">
-      <x:c r="A37" s="7"/>
-      <x:c r="B37" s="6"/>
-      <x:c r="C37" s="6"/>
+      <x:c r="A37" s="7" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="B37" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Organic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C37" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Content</x:t>
+        </x:is>
+      </x:c>
       <x:c r="D37" s="6"/>
       <x:c r="E37" s="6"/>
       <x:c r="F37" s="6"/>
-      <x:c r="G37" s="9"/>
-      <x:c r="H37" s="9"/>
-      <x:c r="I37" s="8"/>
+      <x:c r="G37" s="9" t="n">
+        <x:v>1058</x:v>
+      </x:c>
+      <x:c r="H37" s="9" t="n">
+        <x:v>13920</x:v>
+      </x:c>
+      <x:c r="I37" s="8" t="n">
+        <x:v>98000</x:v>
+      </x:c>
       <x:c r="J37" s="8"/>
-      <x:c r="K37" s="8"/>
-      <x:c r="L37" s="8"/>
-      <x:c r="M37" s="8"/>
-      <x:c r="N37" s="8"/>
-      <x:c r="O37" s="8"/>
-      <x:c r="P37" s="8"/>
-      <x:c r="Q37" s="9"/>
+      <x:c r="K37" s="8" t="n">
+        <x:v>4725</x:v>
+      </x:c>
+      <x:c r="L37" s="8" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="M37" s="8" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="N37" s="8" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="O37" s="8" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="P37" s="8" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="Q37" s="9" t="n">
+        <x:v>25056</x:v>
+      </x:c>
       <x:c r="R37" s="9"/>
       <x:c r="S37" s="9"/>
       <x:c r="T37" s="8"/>
       <x:c r="U37" s="8"/>
+      <x:c r="V37" s="12" t="inlineStr">
+        <x:is>
+          <x:t>Organic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W37" s="12"/>
+      <x:c r="X37" s="12" t="inlineStr">
+        <x:is>
+          <x:t>ORGANIC-101</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="38" ht="23" customHeight="1">
       <x:c r="A38" s="7"/>
@@ -3862,6 +5698,9 @@
       <x:c r="S38" s="9"/>
       <x:c r="T38" s="8"/>
       <x:c r="U38" s="8"/>
+      <x:c r="V38" s="12"/>
+      <x:c r="W38" s="12"/>
+      <x:c r="X38" s="12"/>
     </x:row>
     <x:row r="39" ht="23" customHeight="1">
       <x:c r="A39" s="7"/>
@@ -3885,6 +5724,9 @@
       <x:c r="S39" s="9"/>
       <x:c r="T39" s="8"/>
       <x:c r="U39" s="8"/>
+      <x:c r="V39" s="12"/>
+      <x:c r="W39" s="12"/>
+      <x:c r="X39" s="12"/>
     </x:row>
     <x:row r="40" ht="23" customHeight="1">
       <x:c r="A40" s="7"/>
@@ -3908,6 +5750,9 @@
       <x:c r="S40" s="9"/>
       <x:c r="T40" s="8"/>
       <x:c r="U40" s="8"/>
+      <x:c r="V40" s="12"/>
+      <x:c r="W40" s="12"/>
+      <x:c r="X40" s="12"/>
     </x:row>
     <x:row r="41" ht="23" customHeight="1">
       <x:c r="A41" s="7"/>
@@ -3931,6 +5776,9 @@
       <x:c r="S41" s="9"/>
       <x:c r="T41" s="8"/>
       <x:c r="U41" s="8"/>
+      <x:c r="V41" s="12"/>
+      <x:c r="W41" s="12"/>
+      <x:c r="X41" s="12"/>
     </x:row>
     <x:row r="42" ht="23" customHeight="1">
       <x:c r="A42" s="7"/>
@@ -3954,6 +5802,9 @@
       <x:c r="S42" s="9"/>
       <x:c r="T42" s="8"/>
       <x:c r="U42" s="8"/>
+      <x:c r="V42" s="12"/>
+      <x:c r="W42" s="12"/>
+      <x:c r="X42" s="12"/>
     </x:row>
     <x:row r="43" ht="23" customHeight="1">
       <x:c r="A43" s="7"/>
@@ -3977,6 +5828,9 @@
       <x:c r="S43" s="9"/>
       <x:c r="T43" s="8"/>
       <x:c r="U43" s="8"/>
+      <x:c r="V43" s="12"/>
+      <x:c r="W43" s="12"/>
+      <x:c r="X43" s="12"/>
     </x:row>
     <x:row r="44" ht="23" customHeight="1">
       <x:c r="A44" s="7"/>
@@ -4000,6 +5854,9 @@
       <x:c r="S44" s="9"/>
       <x:c r="T44" s="8"/>
       <x:c r="U44" s="8"/>
+      <x:c r="V44" s="12"/>
+      <x:c r="W44" s="12"/>
+      <x:c r="X44" s="12"/>
     </x:row>
     <x:row r="45" ht="23" customHeight="1">
       <x:c r="A45" s="7"/>
@@ -4023,6 +5880,9 @@
       <x:c r="S45" s="9"/>
       <x:c r="T45" s="8"/>
       <x:c r="U45" s="8"/>
+      <x:c r="V45" s="12"/>
+      <x:c r="W45" s="12"/>
+      <x:c r="X45" s="12"/>
     </x:row>
     <x:row r="46" ht="23" customHeight="1">
       <x:c r="A46" s="7"/>
@@ -4046,6 +5906,9 @@
       <x:c r="S46" s="9"/>
       <x:c r="T46" s="8"/>
       <x:c r="U46" s="8"/>
+      <x:c r="V46" s="12"/>
+      <x:c r="W46" s="12"/>
+      <x:c r="X46" s="12"/>
     </x:row>
     <x:row r="47" ht="23" customHeight="1">
       <x:c r="A47" s="7"/>
@@ -4069,6 +5932,9 @@
       <x:c r="S47" s="9"/>
       <x:c r="T47" s="8"/>
       <x:c r="U47" s="8"/>
+      <x:c r="V47" s="12"/>
+      <x:c r="W47" s="12"/>
+      <x:c r="X47" s="12"/>
     </x:row>
     <x:row r="48" ht="23" customHeight="1">
       <x:c r="A48" s="7"/>
@@ -4092,6 +5958,9 @@
       <x:c r="S48" s="9"/>
       <x:c r="T48" s="8"/>
       <x:c r="U48" s="8"/>
+      <x:c r="V48" s="12"/>
+      <x:c r="W48" s="12"/>
+      <x:c r="X48" s="12"/>
     </x:row>
     <x:row r="49" ht="23" customHeight="1">
       <x:c r="A49" s="7"/>
@@ -4115,6 +5984,9 @@
       <x:c r="S49" s="9"/>
       <x:c r="T49" s="8"/>
       <x:c r="U49" s="8"/>
+      <x:c r="V49" s="12"/>
+      <x:c r="W49" s="12"/>
+      <x:c r="X49" s="12"/>
     </x:row>
     <x:row r="50" ht="23" customHeight="1">
       <x:c r="A50" s="7"/>
@@ -4138,6 +6010,9 @@
       <x:c r="S50" s="9"/>
       <x:c r="T50" s="8"/>
       <x:c r="U50" s="8"/>
+      <x:c r="V50" s="12"/>
+      <x:c r="W50" s="12"/>
+      <x:c r="X50" s="12"/>
     </x:row>
     <x:row r="51" ht="23" customHeight="1">
       <x:c r="A51" s="7"/>
@@ -4161,6 +6036,9 @@
       <x:c r="S51" s="9"/>
       <x:c r="T51" s="8"/>
       <x:c r="U51" s="8"/>
+      <x:c r="V51" s="12"/>
+      <x:c r="W51" s="12"/>
+      <x:c r="X51" s="12"/>
     </x:row>
     <x:row r="52" ht="23" customHeight="1">
       <x:c r="A52" s="7"/>
@@ -4184,6 +6062,9 @@
       <x:c r="S52" s="9"/>
       <x:c r="T52" s="8"/>
       <x:c r="U52" s="8"/>
+      <x:c r="V52" s="12"/>
+      <x:c r="W52" s="12"/>
+      <x:c r="X52" s="12"/>
     </x:row>
     <x:row r="53" ht="23" customHeight="1">
       <x:c r="A53" s="7"/>
@@ -4207,6 +6088,9 @@
       <x:c r="S53" s="9"/>
       <x:c r="T53" s="8"/>
       <x:c r="U53" s="8"/>
+      <x:c r="V53" s="12"/>
+      <x:c r="W53" s="12"/>
+      <x:c r="X53" s="12"/>
     </x:row>
     <x:row r="54" ht="23" customHeight="1">
       <x:c r="A54" s="7"/>
@@ -4230,6 +6114,9 @@
       <x:c r="S54" s="9"/>
       <x:c r="T54" s="8"/>
       <x:c r="U54" s="8"/>
+      <x:c r="V54" s="12"/>
+      <x:c r="W54" s="12"/>
+      <x:c r="X54" s="12"/>
     </x:row>
     <x:row r="55" ht="23" customHeight="1">
       <x:c r="A55" s="7"/>
@@ -4253,6 +6140,9 @@
       <x:c r="S55" s="9"/>
       <x:c r="T55" s="8"/>
       <x:c r="U55" s="8"/>
+      <x:c r="V55" s="12"/>
+      <x:c r="W55" s="12"/>
+      <x:c r="X55" s="12"/>
     </x:row>
     <x:row r="56" ht="23" customHeight="1">
       <x:c r="A56" s="7"/>
@@ -4276,6 +6166,9 @@
       <x:c r="S56" s="9"/>
       <x:c r="T56" s="8"/>
       <x:c r="U56" s="8"/>
+      <x:c r="V56" s="12"/>
+      <x:c r="W56" s="12"/>
+      <x:c r="X56" s="12"/>
     </x:row>
     <x:row r="57" ht="23" customHeight="1">
       <x:c r="A57" s="7"/>
@@ -4299,6 +6192,9 @@
       <x:c r="S57" s="9"/>
       <x:c r="T57" s="8"/>
       <x:c r="U57" s="8"/>
+      <x:c r="V57" s="12"/>
+      <x:c r="W57" s="12"/>
+      <x:c r="X57" s="12"/>
     </x:row>
     <x:row r="58" ht="23" customHeight="1">
       <x:c r="A58" s="7"/>
@@ -4322,6 +6218,9 @@
       <x:c r="S58" s="9"/>
       <x:c r="T58" s="8"/>
       <x:c r="U58" s="8"/>
+      <x:c r="V58" s="12"/>
+      <x:c r="W58" s="12"/>
+      <x:c r="X58" s="12"/>
     </x:row>
     <x:row r="59" ht="23" customHeight="1">
       <x:c r="A59" s="7"/>
@@ -4345,6 +6244,9 @@
       <x:c r="S59" s="9"/>
       <x:c r="T59" s="8"/>
       <x:c r="U59" s="8"/>
+      <x:c r="V59" s="12"/>
+      <x:c r="W59" s="12"/>
+      <x:c r="X59" s="12"/>
     </x:row>
     <x:row r="60" ht="23" customHeight="1">
       <x:c r="A60" s="7"/>
@@ -4368,6 +6270,9 @@
       <x:c r="S60" s="9"/>
       <x:c r="T60" s="8"/>
       <x:c r="U60" s="8"/>
+      <x:c r="V60" s="12"/>
+      <x:c r="W60" s="12"/>
+      <x:c r="X60" s="12"/>
     </x:row>
     <x:row r="61" ht="23" customHeight="1">
       <x:c r="A61" s="7"/>
@@ -4391,6 +6296,9 @@
       <x:c r="S61" s="9"/>
       <x:c r="T61" s="8"/>
       <x:c r="U61" s="8"/>
+      <x:c r="V61" s="12"/>
+      <x:c r="W61" s="12"/>
+      <x:c r="X61" s="12"/>
     </x:row>
     <x:row r="62" ht="23" customHeight="1">
       <x:c r="A62" s="7"/>
@@ -4414,6 +6322,9 @@
       <x:c r="S62" s="9"/>
       <x:c r="T62" s="8"/>
       <x:c r="U62" s="8"/>
+      <x:c r="V62" s="12"/>
+      <x:c r="W62" s="12"/>
+      <x:c r="X62" s="12"/>
     </x:row>
     <x:row r="63" ht="23" customHeight="1">
       <x:c r="A63" s="7"/>
@@ -4437,6 +6348,9 @@
       <x:c r="S63" s="9"/>
       <x:c r="T63" s="8"/>
       <x:c r="U63" s="8"/>
+      <x:c r="V63" s="12"/>
+      <x:c r="W63" s="12"/>
+      <x:c r="X63" s="12"/>
     </x:row>
     <x:row r="64" ht="23" customHeight="1">
       <x:c r="A64" s="7"/>
@@ -4460,6 +6374,9 @@
       <x:c r="S64" s="9"/>
       <x:c r="T64" s="8"/>
       <x:c r="U64" s="8"/>
+      <x:c r="V64" s="12"/>
+      <x:c r="W64" s="12"/>
+      <x:c r="X64" s="12"/>
     </x:row>
     <x:row r="65" ht="23" customHeight="1">
       <x:c r="A65" s="7"/>
@@ -4483,6 +6400,9 @@
       <x:c r="S65" s="9"/>
       <x:c r="T65" s="8"/>
       <x:c r="U65" s="8"/>
+      <x:c r="V65" s="12"/>
+      <x:c r="W65" s="12"/>
+      <x:c r="X65" s="12"/>
     </x:row>
     <x:row r="66" ht="23" customHeight="1">
       <x:c r="A66" s="7"/>
@@ -4506,6 +6426,9 @@
       <x:c r="S66" s="9"/>
       <x:c r="T66" s="8"/>
       <x:c r="U66" s="8"/>
+      <x:c r="V66" s="12"/>
+      <x:c r="W66" s="12"/>
+      <x:c r="X66" s="12"/>
     </x:row>
     <x:row r="67" ht="23" customHeight="1">
       <x:c r="A67" s="7"/>
@@ -4529,6 +6452,9 @@
       <x:c r="S67" s="9"/>
       <x:c r="T67" s="8"/>
       <x:c r="U67" s="8"/>
+      <x:c r="V67" s="12"/>
+      <x:c r="W67" s="12"/>
+      <x:c r="X67" s="12"/>
     </x:row>
     <x:row r="68" ht="23" customHeight="1">
       <x:c r="A68" s="7"/>
@@ -4552,6 +6478,9 @@
       <x:c r="S68" s="9"/>
       <x:c r="T68" s="8"/>
       <x:c r="U68" s="8"/>
+      <x:c r="V68" s="12"/>
+      <x:c r="W68" s="12"/>
+      <x:c r="X68" s="12"/>
     </x:row>
     <x:row r="69" ht="23" customHeight="1">
       <x:c r="A69" s="7"/>
@@ -4575,6 +6504,9 @@
       <x:c r="S69" s="9"/>
       <x:c r="T69" s="8"/>
       <x:c r="U69" s="8"/>
+      <x:c r="V69" s="12"/>
+      <x:c r="W69" s="12"/>
+      <x:c r="X69" s="12"/>
     </x:row>
     <x:row r="70" ht="23" customHeight="1">
       <x:c r="A70" s="7"/>
@@ -4598,6 +6530,9 @@
       <x:c r="S70" s="9"/>
       <x:c r="T70" s="8"/>
       <x:c r="U70" s="8"/>
+      <x:c r="V70" s="12"/>
+      <x:c r="W70" s="12"/>
+      <x:c r="X70" s="12"/>
     </x:row>
     <x:row r="71" ht="23" customHeight="1">
       <x:c r="A71" s="7"/>
@@ -4621,6 +6556,9 @@
       <x:c r="S71" s="9"/>
       <x:c r="T71" s="8"/>
       <x:c r="U71" s="8"/>
+      <x:c r="V71" s="12"/>
+      <x:c r="W71" s="12"/>
+      <x:c r="X71" s="12"/>
     </x:row>
     <x:row r="72" ht="23" customHeight="1">
       <x:c r="A72" s="7"/>
@@ -4644,6 +6582,9 @@
       <x:c r="S72" s="9"/>
       <x:c r="T72" s="8"/>
       <x:c r="U72" s="8"/>
+      <x:c r="V72" s="12"/>
+      <x:c r="W72" s="12"/>
+      <x:c r="X72" s="12"/>
     </x:row>
     <x:row r="73" ht="23" customHeight="1">
       <x:c r="A73" s="7"/>
@@ -4667,6 +6608,9 @@
       <x:c r="S73" s="9"/>
       <x:c r="T73" s="8"/>
       <x:c r="U73" s="8"/>
+      <x:c r="V73" s="12"/>
+      <x:c r="W73" s="12"/>
+      <x:c r="X73" s="12"/>
     </x:row>
     <x:row r="74" ht="23" customHeight="1">
       <x:c r="A74" s="7"/>
@@ -4690,6 +6634,9 @@
       <x:c r="S74" s="9"/>
       <x:c r="T74" s="8"/>
       <x:c r="U74" s="8"/>
+      <x:c r="V74" s="12"/>
+      <x:c r="W74" s="12"/>
+      <x:c r="X74" s="12"/>
     </x:row>
     <x:row r="75" ht="23" customHeight="1">
       <x:c r="A75" s="7"/>
@@ -4713,6 +6660,9 @@
       <x:c r="S75" s="9"/>
       <x:c r="T75" s="8"/>
       <x:c r="U75" s="8"/>
+      <x:c r="V75" s="12"/>
+      <x:c r="W75" s="12"/>
+      <x:c r="X75" s="12"/>
     </x:row>
     <x:row r="76" ht="23" customHeight="1">
       <x:c r="A76" s="7"/>
@@ -4736,6 +6686,9 @@
       <x:c r="S76" s="9"/>
       <x:c r="T76" s="8"/>
       <x:c r="U76" s="8"/>
+      <x:c r="V76" s="12"/>
+      <x:c r="W76" s="12"/>
+      <x:c r="X76" s="12"/>
     </x:row>
     <x:row r="77" ht="23" customHeight="1">
       <x:c r="A77" s="7"/>
@@ -4759,6 +6712,9 @@
       <x:c r="S77" s="9"/>
       <x:c r="T77" s="8"/>
       <x:c r="U77" s="8"/>
+      <x:c r="V77" s="12"/>
+      <x:c r="W77" s="12"/>
+      <x:c r="X77" s="12"/>
     </x:row>
     <x:row r="78" ht="23" customHeight="1">
       <x:c r="A78" s="7"/>
@@ -4782,6 +6738,9 @@
       <x:c r="S78" s="9"/>
       <x:c r="T78" s="8"/>
       <x:c r="U78" s="8"/>
+      <x:c r="V78" s="12"/>
+      <x:c r="W78" s="12"/>
+      <x:c r="X78" s="12"/>
     </x:row>
     <x:row r="79" ht="23" customHeight="1">
       <x:c r="A79" s="7"/>
@@ -4805,6 +6764,9 @@
       <x:c r="S79" s="9"/>
       <x:c r="T79" s="8"/>
       <x:c r="U79" s="8"/>
+      <x:c r="V79" s="12"/>
+      <x:c r="W79" s="12"/>
+      <x:c r="X79" s="12"/>
     </x:row>
     <x:row r="80" ht="23" customHeight="1">
       <x:c r="A80" s="7"/>
@@ -4828,6 +6790,9 @@
       <x:c r="S80" s="9"/>
       <x:c r="T80" s="8"/>
       <x:c r="U80" s="8"/>
+      <x:c r="V80" s="12"/>
+      <x:c r="W80" s="12"/>
+      <x:c r="X80" s="12"/>
     </x:row>
     <x:row r="81" ht="23" customHeight="1">
       <x:c r="A81" s="7"/>
@@ -4851,6 +6816,9 @@
       <x:c r="S81" s="9"/>
       <x:c r="T81" s="8"/>
       <x:c r="U81" s="8"/>
+      <x:c r="V81" s="12"/>
+      <x:c r="W81" s="12"/>
+      <x:c r="X81" s="12"/>
     </x:row>
     <x:row r="82" ht="23" customHeight="1">
       <x:c r="A82" s="7"/>
@@ -4874,6 +6842,9 @@
       <x:c r="S82" s="9"/>
       <x:c r="T82" s="8"/>
       <x:c r="U82" s="8"/>
+      <x:c r="V82" s="12"/>
+      <x:c r="W82" s="12"/>
+      <x:c r="X82" s="12"/>
     </x:row>
     <x:row r="83" ht="23" customHeight="1">
       <x:c r="A83" s="7"/>
@@ -4897,6 +6868,9 @@
       <x:c r="S83" s="9"/>
       <x:c r="T83" s="8"/>
       <x:c r="U83" s="8"/>
+      <x:c r="V83" s="12"/>
+      <x:c r="W83" s="12"/>
+      <x:c r="X83" s="12"/>
     </x:row>
     <x:row r="84" ht="23" customHeight="1">
       <x:c r="A84" s="7"/>
@@ -4920,6 +6894,9 @@
       <x:c r="S84" s="9"/>
       <x:c r="T84" s="8"/>
       <x:c r="U84" s="8"/>
+      <x:c r="V84" s="12"/>
+      <x:c r="W84" s="12"/>
+      <x:c r="X84" s="12"/>
     </x:row>
     <x:row r="85" ht="23" customHeight="1">
       <x:c r="A85" s="7"/>
@@ -4943,6 +6920,9 @@
       <x:c r="S85" s="9"/>
       <x:c r="T85" s="8"/>
       <x:c r="U85" s="8"/>
+      <x:c r="V85" s="12"/>
+      <x:c r="W85" s="12"/>
+      <x:c r="X85" s="12"/>
     </x:row>
     <x:row r="86" ht="23" customHeight="1">
       <x:c r="A86" s="7"/>
@@ -4966,6 +6946,9 @@
       <x:c r="S86" s="9"/>
       <x:c r="T86" s="8"/>
       <x:c r="U86" s="8"/>
+      <x:c r="V86" s="12"/>
+      <x:c r="W86" s="12"/>
+      <x:c r="X86" s="12"/>
     </x:row>
     <x:row r="87" ht="23" customHeight="1">
       <x:c r="A87" s="7"/>
@@ -4989,6 +6972,9 @@
       <x:c r="S87" s="9"/>
       <x:c r="T87" s="8"/>
       <x:c r="U87" s="8"/>
+      <x:c r="V87" s="12"/>
+      <x:c r="W87" s="12"/>
+      <x:c r="X87" s="12"/>
     </x:row>
     <x:row r="88" ht="23" customHeight="1">
       <x:c r="A88" s="7"/>
@@ -5012,6 +6998,9 @@
       <x:c r="S88" s="9"/>
       <x:c r="T88" s="8"/>
       <x:c r="U88" s="8"/>
+      <x:c r="V88" s="12"/>
+      <x:c r="W88" s="12"/>
+      <x:c r="X88" s="12"/>
     </x:row>
     <x:row r="89" ht="23" customHeight="1">
       <x:c r="A89" s="7"/>
@@ -5035,6 +7024,9 @@
       <x:c r="S89" s="9"/>
       <x:c r="T89" s="8"/>
       <x:c r="U89" s="8"/>
+      <x:c r="V89" s="12"/>
+      <x:c r="W89" s="12"/>
+      <x:c r="X89" s="12"/>
     </x:row>
     <x:row r="90" ht="23" customHeight="1">
       <x:c r="A90" s="7"/>
@@ -5058,6 +7050,9 @@
       <x:c r="S90" s="9"/>
       <x:c r="T90" s="8"/>
       <x:c r="U90" s="8"/>
+      <x:c r="V90" s="12"/>
+      <x:c r="W90" s="12"/>
+      <x:c r="X90" s="12"/>
     </x:row>
     <x:row r="91" ht="23" customHeight="1">
       <x:c r="A91" s="7"/>
@@ -5081,6 +7076,9 @@
       <x:c r="S91" s="9"/>
       <x:c r="T91" s="8"/>
       <x:c r="U91" s="8"/>
+      <x:c r="V91" s="12"/>
+      <x:c r="W91" s="12"/>
+      <x:c r="X91" s="12"/>
     </x:row>
     <x:row r="92" ht="23" customHeight="1">
       <x:c r="A92" s="7"/>
@@ -5104,6 +7102,9 @@
       <x:c r="S92" s="9"/>
       <x:c r="T92" s="8"/>
       <x:c r="U92" s="8"/>
+      <x:c r="V92" s="12"/>
+      <x:c r="W92" s="12"/>
+      <x:c r="X92" s="12"/>
     </x:row>
     <x:row r="93" ht="23" customHeight="1">
       <x:c r="A93" s="7"/>
@@ -5127,6 +7128,9 @@
       <x:c r="S93" s="9"/>
       <x:c r="T93" s="8"/>
       <x:c r="U93" s="8"/>
+      <x:c r="V93" s="12"/>
+      <x:c r="W93" s="12"/>
+      <x:c r="X93" s="12"/>
     </x:row>
     <x:row r="94" ht="23" customHeight="1">
       <x:c r="A94" s="7"/>
@@ -5150,6 +7154,9 @@
       <x:c r="S94" s="9"/>
       <x:c r="T94" s="8"/>
       <x:c r="U94" s="8"/>
+      <x:c r="V94" s="12"/>
+      <x:c r="W94" s="12"/>
+      <x:c r="X94" s="12"/>
     </x:row>
     <x:row r="95" ht="23" customHeight="1">
       <x:c r="A95" s="7"/>
@@ -5173,6 +7180,9 @@
       <x:c r="S95" s="9"/>
       <x:c r="T95" s="8"/>
       <x:c r="U95" s="8"/>
+      <x:c r="V95" s="12"/>
+      <x:c r="W95" s="12"/>
+      <x:c r="X95" s="12"/>
     </x:row>
     <x:row r="96" ht="23" customHeight="1">
       <x:c r="A96" s="7"/>
@@ -5196,6 +7206,9 @@
       <x:c r="S96" s="9"/>
       <x:c r="T96" s="8"/>
       <x:c r="U96" s="8"/>
+      <x:c r="V96" s="12"/>
+      <x:c r="W96" s="12"/>
+      <x:c r="X96" s="12"/>
     </x:row>
     <x:row r="97" ht="23" customHeight="1">
       <x:c r="A97" s="7"/>
@@ -5219,6 +7232,9 @@
       <x:c r="S97" s="9"/>
       <x:c r="T97" s="8"/>
       <x:c r="U97" s="8"/>
+      <x:c r="V97" s="12"/>
+      <x:c r="W97" s="12"/>
+      <x:c r="X97" s="12"/>
     </x:row>
     <x:row r="98" ht="23" customHeight="1">
       <x:c r="A98" s="7"/>
@@ -5242,6 +7258,9 @@
       <x:c r="S98" s="9"/>
       <x:c r="T98" s="8"/>
       <x:c r="U98" s="8"/>
+      <x:c r="V98" s="12"/>
+      <x:c r="W98" s="12"/>
+      <x:c r="X98" s="12"/>
     </x:row>
     <x:row r="99" ht="23" customHeight="1">
       <x:c r="A99" s="7"/>
@@ -5265,6 +7284,9 @@
       <x:c r="S99" s="9"/>
       <x:c r="T99" s="8"/>
       <x:c r="U99" s="8"/>
+      <x:c r="V99" s="12"/>
+      <x:c r="W99" s="12"/>
+      <x:c r="X99" s="12"/>
     </x:row>
     <x:row r="100" ht="23" customHeight="1">
       <x:c r="A100" s="7"/>
@@ -5288,6 +7310,9 @@
       <x:c r="S100" s="9"/>
       <x:c r="T100" s="8"/>
       <x:c r="U100" s="8"/>
+      <x:c r="V100" s="12"/>
+      <x:c r="W100" s="12"/>
+      <x:c r="X100" s="12"/>
     </x:row>
     <x:row r="101" ht="23" customHeight="1">
       <x:c r="A101" s="7"/>
@@ -5311,11 +7336,14 @@
       <x:c r="S101" s="9"/>
       <x:c r="T101" s="8"/>
       <x:c r="U101" s="8"/>
+      <x:c r="V101" s="12"/>
+      <x:c r="W101" s="12"/>
+      <x:c r="X101" s="12"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc39fc28be6af493e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c1aac98df24fc0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5353,80 +7381,80 @@
       <x:c r="D3" s="1"/>
     </x:row>
     <x:row r="4" ht="58" customHeight="1">
-      <x:c r="A4" s="12" t="str">
+      <x:c r="A4" s="13" t="str">
         <x:v>1. Enter data</x:v>
       </x:c>
-      <x:c r="B4" s="13" t="str">
+      <x:c r="B4" s="14" t="str">
         <x:v>Keep the headers in row 1. Start your data in row 2 on the Marketing data sheet.</x:v>
       </x:c>
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
-      <x:c r="A5" s="12" t="str">
+      <x:c r="A5" s="13" t="str">
         <x:v>2. Define each row</x:v>
       </x:c>
-      <x:c r="B5" s="13" t="str">
+      <x:c r="B5" s="14" t="str">
         <x:v>Use one row per date, channel and campaign (plus creative, region or product if needed). Do not add total rows or duplicate the same results.</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1"/>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
-      <x:c r="A6" s="12" t="str">
+      <x:c r="A6" s="13" t="str">
         <x:v>3. Include a comparison</x:v>
       </x:c>
-      <x:c r="B6" s="13" t="str">
+      <x:c r="B6" s="14" t="str">
         <x:v>Add at least two calendar months to compare performance. Use consistent reporting periods and definitions.</x:v>
       </x:c>
       <x:c r="C6" s="1"/>
       <x:c r="D6" s="1"/>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
-      <x:c r="A7" s="12" t="str">
+      <x:c r="A7" s="13" t="str">
         <x:v>4. Leave unknowns blank</x:v>
       </x:c>
-      <x:c r="B7" s="13" t="str">
+      <x:c r="B7" s="14" t="str">
         <x:v>Fill only metrics you have. A blank means unavailable; zero means you measured a genuine zero. Date, Channel, Spend and Revenue are recommended, not mandatory.</x:v>
       </x:c>
       <x:c r="C7" s="1"/>
       <x:c r="D7" s="1"/>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
-      <x:c r="A8" s="12" t="str">
+      <x:c r="A8" s="13" t="str">
         <x:v>5. Use the correct units</x:v>
       </x:c>
-      <x:c r="B8" s="13" t="str">
+      <x:c r="B8" s="14" t="str">
         <x:v>Enter financial values in GBP and counts as numbers. Keep dates typed and displayed as yyyy-mm-dd. CTR, CPC, CPA/CAC, ROAS and conversion rates are calculated by Lens.</x:v>
       </x:c>
       <x:c r="C8" s="1"/>
       <x:c r="D8" s="1"/>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
-      <x:c r="A9" s="12" t="str">
+      <x:c r="A9" s="13" t="str">
         <x:v>6. Save and upload</x:v>
       </x:c>
-      <x:c r="B9" s="13" t="str">
+      <x:c r="B9" s="14" t="str">
         <x:v>Save as XLSX, upload to Lens and select Marketing data. You can add more rows beyond the 100 prepared rows.</x:v>
       </x:c>
       <x:c r="C9" s="1"/>
       <x:c r="D9" s="1"/>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
-      <x:c r="A10" s="12" t="str">
+      <x:c r="A10" s="13" t="str">
         <x:v>Example data</x:v>
       </x:c>
-      <x:c r="B10" s="13" t="str">
-        <x:v>The separate Example data sheet contains fictional figures. It is not part of your analysis. Do not copy it into your input sheet unless replacing every example value.</x:v>
+      <x:c r="B10" s="14" t="str">
+        <x:v>The Example data sheet contains the fictional sample dataset used in the Lens demo. It is provided for reference and is not included in analysis unless you copy or upload it as input.</x:v>
       </x:c>
       <x:c r="C10" s="1"/>
       <x:c r="D10" s="1"/>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
-      <x:c r="A11" s="12" t="str">
+      <x:c r="A11" s="13" t="str">
         <x:v>Input cells</x:v>
       </x:c>
-      <x:c r="B11" s="13" t="str">
+      <x:c r="B11" s="14" t="str">
         <x:v>Pale yellow cells are ready for your data. Optional columns may remain blank or be removed.</x:v>
       </x:c>
       <x:c r="C11" s="1"/>
@@ -5453,312 +7481,354 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="45" customHeight="1">
-      <x:c r="A14" s="13" t="str">
+      <x:c r="A14" s="14" t="str">
         <x:v>Date</x:v>
       </x:c>
-      <x:c r="B14" s="13" t="str">
+      <x:c r="B14" s="14" t="str">
         <x:v>Date</x:v>
       </x:c>
-      <x:c r="C14" s="13" t="str">
+      <x:c r="C14" s="14" t="str">
         <x:v>2026-09-30</x:v>
       </x:c>
-      <x:c r="D14" s="13" t="str">
+      <x:c r="D14" s="14" t="str">
         <x:v>Use a real date. For monthly totals, use the month-end date.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="45" customHeight="1">
-      <x:c r="A15" s="13" t="str">
+      <x:c r="A15" s="14" t="str">
         <x:v>Channel</x:v>
       </x:c>
-      <x:c r="B15" s="13" t="str">
+      <x:c r="B15" s="14" t="str">
         <x:v>Text</x:v>
       </x:c>
-      <x:c r="C15" s="13" t="str">
+      <x:c r="C15" s="14" t="str">
         <x:v>Paid search</x:v>
       </x:c>
-      <x:c r="D15" s="13" t="str">
+      <x:c r="D15" s="14" t="str">
         <x:v>Use consistent names, such as Paid search, Paid social, Email or Organic.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="45" customHeight="1">
-      <x:c r="A16" s="13" t="str">
+      <x:c r="A16" s="14" t="str">
         <x:v>Campaign</x:v>
       </x:c>
-      <x:c r="B16" s="13" t="str">
+      <x:c r="B16" s="14" t="str">
         <x:v>Text</x:v>
       </x:c>
-      <x:c r="C16" s="13" t="str">
+      <x:c r="C16" s="14" t="str">
         <x:v>Brand search</x:v>
       </x:c>
-      <x:c r="D16" s="13" t="str">
+      <x:c r="D16" s="14" t="str">
         <x:v>Campaign name; optional.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="45" customHeight="1">
-      <x:c r="A17" s="13" t="str">
+      <x:c r="A17" s="14" t="str">
         <x:v>Creative</x:v>
       </x:c>
-      <x:c r="B17" s="13" t="str">
+      <x:c r="B17" s="14" t="str">
         <x:v>Text</x:v>
       </x:c>
-      <x:c r="C17" s="13" t="str">
+      <x:c r="C17" s="14" t="str">
         <x:v>Video A</x:v>
       </x:c>
-      <x:c r="D17" s="13" t="str">
+      <x:c r="D17" s="14" t="str">
         <x:v>Creative asset, format or message; optional. Enables creative comparison.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="45" customHeight="1">
-      <x:c r="A18" s="13" t="str">
+      <x:c r="A18" s="14" t="str">
         <x:v>Region</x:v>
       </x:c>
-      <x:c r="B18" s="13" t="str">
+      <x:c r="B18" s="14" t="str">
         <x:v>Text</x:v>
       </x:c>
-      <x:c r="C18" s="13" t="str">
+      <x:c r="C18" s="14" t="str">
         <x:v>UK</x:v>
       </x:c>
-      <x:c r="D18" s="13" t="str">
+      <x:c r="D18" s="14" t="str">
         <x:v>Region or country; optional.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="45" customHeight="1">
-      <x:c r="A19" s="13" t="str">
+      <x:c r="A19" s="14" t="str">
         <x:v>Product</x:v>
       </x:c>
-      <x:c r="B19" s="13" t="str">
+      <x:c r="B19" s="14" t="str">
         <x:v>Text</x:v>
       </x:c>
-      <x:c r="C19" s="13" t="str">
+      <x:c r="C19" s="14" t="str">
         <x:v>Subscription</x:v>
       </x:c>
-      <x:c r="D19" s="13" t="str">
+      <x:c r="D19" s="14" t="str">
         <x:v>Product or service; optional.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="45" customHeight="1">
-      <x:c r="A20" s="13" t="str">
+      <x:c r="A20" s="14" t="str">
         <x:v>Spend</x:v>
       </x:c>
-      <x:c r="B20" s="13" t="str">
+      <x:c r="B20" s="14" t="str">
         <x:v>GBP</x:v>
       </x:c>
-      <x:c r="C20" s="13" t="n">
+      <x:c r="C20" s="14" t="n">
         <x:v>1500</x:v>
       </x:c>
-      <x:c r="D20" s="13" t="str">
+      <x:c r="D20" s="14" t="str">
         <x:v>Marketing spend for this row. Enter numbers without currency symbols.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="45" customHeight="1">
-      <x:c r="A21" s="13" t="str">
+      <x:c r="A21" s="14" t="str">
         <x:v>Revenue</x:v>
       </x:c>
-      <x:c r="B21" s="13" t="str">
+      <x:c r="B21" s="14" t="str">
         <x:v>GBP</x:v>
       </x:c>
-      <x:c r="C21" s="13" t="n">
+      <x:c r="C21" s="14" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D21" s="13" t="str">
+      <x:c r="D21" s="14" t="str">
         <x:v>Recorded revenue for this row; attribution must be consistent.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="45" customHeight="1">
-      <x:c r="A22" s="13" t="str">
+      <x:c r="A22" s="14" t="str">
         <x:v>Impressions</x:v>
       </x:c>
-      <x:c r="B22" s="13" t="str">
+      <x:c r="B22" s="14" t="str">
         <x:v>Whole number</x:v>
       </x:c>
-      <x:c r="C22" s="13" t="n">
+      <x:c r="C22" s="14" t="n">
         <x:v>50000</x:v>
       </x:c>
-      <x:c r="D22" s="13" t="str">
+      <x:c r="D22" s="14" t="str">
         <x:v>Number of ad impressions.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="45" customHeight="1">
-      <x:c r="A23" s="13" t="str">
+      <x:c r="A23" s="14" t="str">
         <x:v>Reach</x:v>
       </x:c>
-      <x:c r="B23" s="13" t="str">
+      <x:c r="B23" s="14" t="str">
         <x:v>Whole number</x:v>
       </x:c>
-      <x:c r="C23" s="13" t="n">
+      <x:c r="C23" s="14" t="n">
         <x:v>35000</x:v>
       </x:c>
-      <x:c r="D23" s="13" t="str">
+      <x:c r="D23" s="14" t="str">
         <x:v>Unique people reached; may overlap across rows and channels.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="45" customHeight="1">
-      <x:c r="A24" s="13" t="str">
+      <x:c r="A24" s="14" t="str">
         <x:v>Clicks</x:v>
       </x:c>
-      <x:c r="B24" s="13" t="str">
+      <x:c r="B24" s="14" t="str">
         <x:v>Whole number</x:v>
       </x:c>
-      <x:c r="C24" s="13" t="n">
+      <x:c r="C24" s="14" t="n">
         <x:v>1500</x:v>
       </x:c>
-      <x:c r="D24" s="13" t="str">
+      <x:c r="D24" s="14" t="str">
         <x:v>Clicks using the same definition in each period.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="45" customHeight="1">
-      <x:c r="A25" s="13" t="str">
+      <x:c r="A25" s="14" t="str">
         <x:v>Leads</x:v>
       </x:c>
-      <x:c r="B25" s="13" t="str">
+      <x:c r="B25" s="14" t="str">
         <x:v>Whole number</x:v>
       </x:c>
-      <x:c r="C25" s="13" t="n">
+      <x:c r="C25" s="14" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D25" s="13" t="str">
+      <x:c r="D25" s="14" t="str">
         <x:v>New leads generated.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="45" customHeight="1">
-      <x:c r="A26" s="13" t="str">
+      <x:c r="A26" s="14" t="str">
         <x:v>MQLs</x:v>
       </x:c>
-      <x:c r="B26" s="13" t="str">
+      <x:c r="B26" s="14" t="str">
         <x:v>Whole number</x:v>
       </x:c>
-      <x:c r="C26" s="13" t="n">
+      <x:c r="C26" s="14" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D26" s="13" t="str">
+      <x:c r="D26" s="14" t="str">
         <x:v>Marketing-qualified leads.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="45" customHeight="1">
-      <x:c r="A27" s="13" t="str">
+      <x:c r="A27" s="14" t="str">
         <x:v>SQLs</x:v>
       </x:c>
-      <x:c r="B27" s="13" t="str">
+      <x:c r="B27" s="14" t="str">
         <x:v>Whole number</x:v>
       </x:c>
-      <x:c r="C27" s="13" t="n">
+      <x:c r="C27" s="14" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D27" s="13" t="str">
+      <x:c r="D27" s="14" t="str">
         <x:v>Sales-qualified leads.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="45" customHeight="1">
-      <x:c r="A28" s="13" t="str">
+      <x:c r="A28" s="14" t="str">
         <x:v>Conversions</x:v>
       </x:c>
-      <x:c r="B28" s="13" t="str">
+      <x:c r="B28" s="14" t="str">
         <x:v>Whole number</x:v>
       </x:c>
-      <x:c r="C28" s="13" t="n">
+      <x:c r="C28" s="14" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D28" s="13" t="str">
+      <x:c r="D28" s="14" t="str">
         <x:v>Completed conversion events. Define the event consistently.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="45" customHeight="1">
-      <x:c r="A29" s="13" t="str">
+      <x:c r="A29" s="14" t="str">
         <x:v>Customers</x:v>
       </x:c>
-      <x:c r="B29" s="13" t="str">
+      <x:c r="B29" s="14" t="str">
         <x:v>Whole number</x:v>
       </x:c>
-      <x:c r="C29" s="13" t="n">
+      <x:c r="C29" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D29" s="13" t="str">
+      <x:c r="D29" s="14" t="str">
         <x:v>New customers acquired. This is the denominator used for CAC.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="45" customHeight="1">
-      <x:c r="A30" s="13" t="str">
+      <x:c r="A30" s="14" t="str">
         <x:v>Pipeline</x:v>
       </x:c>
-      <x:c r="B30" s="13" t="str">
+      <x:c r="B30" s="14" t="str">
         <x:v>GBP</x:v>
       </x:c>
-      <x:c r="C30" s="13" t="n">
+      <x:c r="C30" s="14" t="n">
         <x:v>15000</x:v>
       </x:c>
-      <x:c r="D30" s="13" t="str">
+      <x:c r="D30" s="14" t="str">
         <x:v>Pipeline value generated in this period, not repeated cumulative snapshots.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="45" customHeight="1">
-      <x:c r="A31" s="13" t="str">
+      <x:c r="A31" s="14" t="str">
         <x:v>Gross profit</x:v>
       </x:c>
-      <x:c r="B31" s="13" t="str">
+      <x:c r="B31" s="14" t="str">
         <x:v>GBP</x:v>
       </x:c>
-      <x:c r="C31" s="13" t="n">
+      <x:c r="C31" s="14" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="D31" s="13" t="str">
+      <x:c r="D31" s="14" t="str">
         <x:v>Gross profit before marketing spend. Enables (gross profit − spend) ÷ spend ROI.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="45" customHeight="1">
-      <x:c r="A32" s="13" t="str">
+      <x:c r="A32" s="14" t="str">
         <x:v>Budget</x:v>
       </x:c>
-      <x:c r="B32" s="13" t="str">
+      <x:c r="B32" s="14" t="str">
         <x:v>GBP</x:v>
       </x:c>
-      <x:c r="C32" s="13" t="n">
+      <x:c r="C32" s="14" t="n">
         <x:v>1800</x:v>
       </x:c>
-      <x:c r="D32" s="13" t="str">
+      <x:c r="D32" s="14" t="str">
         <x:v>Planned marketing spend for this row; optional.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="45" customHeight="1">
-      <x:c r="A33" s="13" t="str">
+      <x:c r="A33" s="14" t="str">
         <x:v>Email opens</x:v>
       </x:c>
-      <x:c r="B33" s="13" t="str">
+      <x:c r="B33" s="14" t="str">
         <x:v>Whole number</x:v>
       </x:c>
-      <x:c r="C33" s="13" t="n">
+      <x:c r="C33" s="14" t="n">
         <x:v>2500</x:v>
       </x:c>
-      <x:c r="D33" s="13" t="str">
+      <x:c r="D33" s="14" t="str">
         <x:v>Email opens; optional. Keep unique/total definitions consistent.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="45" customHeight="1">
-      <x:c r="A34" s="13" t="str">
+      <x:c r="A34" s="14" t="str">
         <x:v>Website traffic</x:v>
       </x:c>
-      <x:c r="B34" s="13" t="str">
+      <x:c r="B34" s="14" t="str">
         <x:v>Whole number</x:v>
       </x:c>
-      <x:c r="C34" s="13" t="n">
+      <x:c r="C34" s="14" t="n">
         <x:v>3500</x:v>
       </x:c>
-      <x:c r="D34" s="13" t="str">
+      <x:c r="D34" s="14" t="str">
         <x:v>Website sessions; optional. Do not mix sessions with unique users.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="1"/>
-      <x:c r="B35" s="1"/>
-      <x:c r="C35" s="1"/>
-      <x:c r="D35" s="1"/>
+      <x:c r="A35" s="1" t="str">
+        <x:v>Platform</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="str">
+        <x:v>Meta</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="str">
+        <x:v>Advertising platform: Meta, LinkedIn, Google Ads, TikTok or another name.</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="11" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="str">
+        <x:v>Instagram</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="str">
+        <x:v>For Meta, enter Facebook or Instagram. Leave blank if results are combined. Do not upload combined totals alongside the same placement breakdown.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="1" t="str">
+        <x:v>Campaign ID</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="str">
+        <x:v>META-101</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="str">
+        <x:v>Stable identifier for the campaign. Use the same ID across periods and placements.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="1"/>
+      <x:c r="B38" s="1"/>
+      <x:c r="C38" s="1"/>
+      <x:c r="D38" s="1"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="1" t="str">
         <x:v>Important: recorded revenue does not prove marketing attribution. ROAS is not profit.</x:v>
       </x:c>
-      <x:c r="B36" s="1"/>
-      <x:c r="C36" s="1"/>
-      <x:c r="D36" s="1"/>
+      <x:c r="B39" s="1"/>
+      <x:c r="C39" s="1"/>
+      <x:c r="D39" s="1"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
